--- a/files/PRH Orderdatei 1025.xlsx_.xlsx
+++ b/files/PRH Orderdatei 1025.xlsx_.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,32 +425,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MgCode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
@@ -471,7 +459,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>OCT251074</t>
+          <t>OCT251410</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,7 +486,7 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>OCT251075</t>
+          <t>OCT251411</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -525,7 +513,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>OCT251076</t>
+          <t>OCT251412</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,7 +540,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>OCT251077</t>
+          <t>OCT251413</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,7 +567,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>OCT251078</t>
+          <t>OCT251414</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,7 +594,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>OCT251079</t>
+          <t>OCT251415</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -633,7 +621,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>OCT251080</t>
+          <t>OCT251416</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -660,7 +648,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>OCT251081</t>
+          <t>OCT251417</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -687,7 +675,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>OCT251082</t>
+          <t>OCT251418</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +702,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>OCT251083</t>
+          <t>OCT251419</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -741,7 +729,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>OCT251084</t>
+          <t>OCT251420</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -768,7 +756,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>OCT251085</t>
+          <t>OCT251421</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -795,7 +783,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>OCT251086</t>
+          <t>OCT251422</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -822,7 +810,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>OCT251087</t>
+          <t>OCT251423</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -849,7 +837,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>OCT251088</t>
+          <t>OCT251424</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -876,7 +864,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>OCT251089</t>
+          <t>OCT251425</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -903,7 +891,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>OCT251090</t>
+          <t>OCT251426</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -930,7 +918,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>OCT251091</t>
+          <t>OCT251427</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -957,7 +945,7 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>OCT251092</t>
+          <t>OCT251428</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -984,7 +972,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>OCT251093</t>
+          <t>OCT251429</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1011,7 +999,7 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>OCT251094</t>
+          <t>OCT251430</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1038,7 +1026,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>OCT251095</t>
+          <t>OCT251431</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1065,7 +1053,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>OCT251096</t>
+          <t>OCT251432</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1092,7 +1080,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>OCT251097</t>
+          <t>OCT251433</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1119,7 +1107,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>OCT251098</t>
+          <t>OCT251434</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1146,7 +1134,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>OCT251099</t>
+          <t>OCT251435</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,7 +1161,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>OCT251100</t>
+          <t>OCT251436</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1200,7 +1188,7 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>OCT251101</t>
+          <t>OCT251437</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1227,7 +1215,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>OCT251102</t>
+          <t>OCT251438</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1254,7 +1242,7 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>OCT251103</t>
+          <t>OCT251439</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1281,7 +1269,7 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>OCT251104</t>
+          <t>OCT251440</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1308,7 +1296,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>OCT251105</t>
+          <t>OCT251441</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1335,7 +1323,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>OCT251106</t>
+          <t>OCT251442</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1362,7 +1350,7 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>OCT251107</t>
+          <t>OCT251443</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1389,7 +1377,7 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>OCT251108</t>
+          <t>OCT251444</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1416,7 +1404,7 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>OCT251109</t>
+          <t>OCT251445</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1443,7 +1431,7 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>OCT251110</t>
+          <t>OCT251446</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1470,7 +1458,7 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>OCT251111</t>
+          <t>OCT251447</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1497,7 +1485,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>OCT251112</t>
+          <t>OCT251448</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1524,7 +1512,7 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>OCT251113</t>
+          <t>OCT251449</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1551,7 +1539,7 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>OCT251114</t>
+          <t>OCT251450</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1578,7 +1566,7 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>OCT251115</t>
+          <t>OCT251451</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1605,7 +1593,7 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>OCT251116</t>
+          <t>OCT251452</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1632,7 +1620,7 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>OCT251117</t>
+          <t>OCT251453</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1659,7 +1647,7 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>OCT251118</t>
+          <t>OCT251454</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1686,7 +1674,7 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>OCT251119</t>
+          <t>OCT251455</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1713,7 +1701,7 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>OCT251120</t>
+          <t>OCT251456</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1740,7 +1728,7 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>OCT251121</t>
+          <t>OCT251457</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1767,7 +1755,7 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>OCT251122</t>
+          <t>OCT251458</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1794,7 +1782,7 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>OCT251123</t>
+          <t>OCT251459</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1821,7 +1809,7 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>OCT251124</t>
+          <t>OCT251460</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1848,7 +1836,7 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>OCT251125</t>
+          <t>OCT251461</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1875,7 +1863,7 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>OCT251126</t>
+          <t>OCT251462</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1902,7 +1890,7 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>OCT251127</t>
+          <t>OCT251463</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1929,7 +1917,7 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>OCT251128</t>
+          <t>OCT251464</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1956,7 +1944,7 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>OCT251129</t>
+          <t>OCT251465</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1983,7 +1971,7 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>OCT251130</t>
+          <t>OCT251466</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2010,7 +1998,7 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>OCT251131</t>
+          <t>OCT251467</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2037,7 +2025,7 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>OCT251132</t>
+          <t>OCT251468</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2064,7 +2052,7 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>OCT251133</t>
+          <t>OCT251469</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2091,7 +2079,7 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>OCT251134</t>
+          <t>OCT251470</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2118,7 +2106,7 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>OCT251135</t>
+          <t>OCT251471</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2145,7 +2133,7 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>OCT251136</t>
+          <t>OCT251472</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2172,7 +2160,7 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>OCT251137</t>
+          <t>OCT251473</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2199,7 +2187,7 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>OCT251138</t>
+          <t>OCT251474</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2226,7 +2214,7 @@
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>OCT251139</t>
+          <t>OCT251475</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2253,7 +2241,7 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>OCT251140</t>
+          <t>OCT251476</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2280,7 +2268,7 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>OCT251141</t>
+          <t>OCT251477</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2307,7 +2295,7 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>OCT251142</t>
+          <t>OCT251478</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2334,7 +2322,7 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>OCT251143</t>
+          <t>OCT251479</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2361,7 +2349,7 @@
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>OCT251144</t>
+          <t>OCT251480</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2388,7 +2376,7 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>OCT251145</t>
+          <t>OCT251481</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2415,7 +2403,7 @@
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>OCT251146</t>
+          <t>OCT251482</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2442,7 +2430,7 @@
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>OCT251147</t>
+          <t>OCT251483</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2469,7 +2457,7 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>OCT251148</t>
+          <t>OCT251484</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2496,7 +2484,7 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>OCT251149</t>
+          <t>OCT251485</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2523,7 +2511,7 @@
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>OCT251150</t>
+          <t>OCT251486</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2550,7 +2538,7 @@
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>OCT251151</t>
+          <t>OCT251487</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2577,7 +2565,7 @@
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>OCT251152</t>
+          <t>OCT251488</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2604,7 +2592,7 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>OCT251153</t>
+          <t>OCT251489</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2631,7 +2619,7 @@
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>OCT251154</t>
+          <t>OCT251490</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2658,7 +2646,7 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>OCT251155</t>
+          <t>OCT251491</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2685,7 +2673,7 @@
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>OCT251156</t>
+          <t>OCT251492</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2712,7 +2700,7 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>OCT251157</t>
+          <t>OCT251493</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2739,7 +2727,7 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>OCT251158</t>
+          <t>OCT251494</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2766,7 +2754,7 @@
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>OCT251159</t>
+          <t>OCT251495</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2793,7 +2781,7 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>OCT251160</t>
+          <t>OCT251496</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2820,7 +2808,7 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>OCT251161</t>
+          <t>OCT251497</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2847,7 +2835,7 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>OCT251162</t>
+          <t>OCT251498</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2874,7 +2862,7 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>OCT251163</t>
+          <t>OCT251499</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2901,7 +2889,7 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>OCT251164</t>
+          <t>OCT251500</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2928,7 +2916,7 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>OCT251165</t>
+          <t>OCT251501</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2955,7 +2943,7 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>OCT251166</t>
+          <t>OCT251502</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2982,7 +2970,7 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>OCT251167</t>
+          <t>OCT251503</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3009,7 +2997,7 @@
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>OCT251168</t>
+          <t>OCT251504</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3036,7 +3024,7 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>OCT251169</t>
+          <t>OCT251505</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3063,7 +3051,7 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>OCT251170</t>
+          <t>OCT251506</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3090,7 +3078,7 @@
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>OCT251171</t>
+          <t>OCT251507</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3117,7 +3105,7 @@
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>OCT251172</t>
+          <t>OCT251508</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3144,7 +3132,7 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>OCT251173</t>
+          <t>OCT251509</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3171,7 +3159,7 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>OCT251174</t>
+          <t>OCT251510</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3198,7 +3186,7 @@
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>OCT251175</t>
+          <t>OCT251511</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3225,7 +3213,7 @@
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>OCT251176</t>
+          <t>OCT251512</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3252,7 +3240,7 @@
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>OCT251177</t>
+          <t>OCT251513</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3279,7 +3267,7 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>OCT251178</t>
+          <t>OCT251514</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3306,7 +3294,7 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>OCT251179</t>
+          <t>OCT251515</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3333,7 +3321,7 @@
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>OCT251180</t>
+          <t>OCT251516</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3360,7 +3348,7 @@
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>OCT251181</t>
+          <t>OCT251517</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3387,7 +3375,7 @@
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>OCT251182</t>
+          <t>OCT251518</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3414,7 +3402,7 @@
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>OCT251183</t>
+          <t>OCT251519</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3441,7 +3429,7 @@
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t>OCT251184</t>
+          <t>OCT251520</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3468,7 +3456,7 @@
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>OCT251185</t>
+          <t>OCT251521</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3495,7 +3483,7 @@
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>OCT251186</t>
+          <t>OCT251522</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3522,7 +3510,7 @@
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>OCT251187</t>
+          <t>OCT251523</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3549,7 +3537,7 @@
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>OCT251188</t>
+          <t>OCT251524</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3576,7 +3564,7 @@
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>OCT251189</t>
+          <t>OCT251525</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3603,7 +3591,7 @@
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>OCT251190</t>
+          <t>OCT251526</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3630,7 +3618,7 @@
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>OCT251191</t>
+          <t>OCT251527</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3657,7 +3645,7 @@
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>OCT251192</t>
+          <t>OCT251528</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3684,7 +3672,7 @@
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>OCT251193</t>
+          <t>OCT251529</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3711,7 +3699,7 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>OCT251194</t>
+          <t>OCT251530</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3738,7 +3726,7 @@
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>OCT251195</t>
+          <t>OCT251531</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3765,7 +3753,7 @@
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>OCT251196</t>
+          <t>OCT251532</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3792,7 +3780,7 @@
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>OCT251197</t>
+          <t>OCT251533</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3819,7 +3807,7 @@
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>OCT251198</t>
+          <t>OCT251534</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3846,7 +3834,7 @@
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t>OCT251199</t>
+          <t>OCT251535</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3873,7 +3861,7 @@
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>OCT251200</t>
+          <t>OCT251536</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3898,7 +3886,7 @@
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>OCT251201</t>
+          <t>OCT251537</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3925,7 +3913,7 @@
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t>OCT251202</t>
+          <t>OCT251538</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3952,7 +3940,7 @@
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>OCT251203</t>
+          <t>OCT251539</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3979,7 +3967,7 @@
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>OCT251204</t>
+          <t>OCT251540</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4006,7 +3994,7 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>OCT251205</t>
+          <t>OCT251541</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4033,7 +4021,7 @@
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>OCT251206</t>
+          <t>OCT251542</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4060,7 +4048,7 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>OCT251207</t>
+          <t>OCT251543</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4087,7 +4075,7 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>OCT251208</t>
+          <t>OCT251544</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4114,7 +4102,7 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>OCT251209</t>
+          <t>OCT251545</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4141,7 +4129,7 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>OCT251210</t>
+          <t>OCT251546</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4168,7 +4156,7 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>OCT251211</t>
+          <t>OCT251547</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4195,7 +4183,7 @@
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>OCT251212</t>
+          <t>OCT251548</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4222,7 +4210,7 @@
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>OCT251213</t>
+          <t>OCT251549</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4249,7 +4237,7 @@
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t>OCT251214</t>
+          <t>OCT251550</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4276,7 +4264,7 @@
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t>OCT251215</t>
+          <t>OCT251551</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4303,7 +4291,7 @@
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t>OCT251216</t>
+          <t>OCT251552</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4330,7 +4318,7 @@
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t>OCT251217</t>
+          <t>OCT251553</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4357,7 +4345,7 @@
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>OCT251218</t>
+          <t>OCT251554</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4384,7 +4372,7 @@
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>OCT251219</t>
+          <t>OCT251555</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4411,7 +4399,7 @@
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t>OCT251220</t>
+          <t>OCT251556</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4438,7 +4426,7 @@
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t>OCT251221</t>
+          <t>OCT251557</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4465,7 +4453,7 @@
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t>OCT251222</t>
+          <t>OCT251558</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4492,7 +4480,7 @@
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>OCT251223</t>
+          <t>OCT251559</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4519,7 +4507,7 @@
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>OCT251224</t>
+          <t>OCT251560</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4546,7 +4534,7 @@
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>OCT251225</t>
+          <t>OCT251561</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4573,7 +4561,7 @@
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>OCT251226</t>
+          <t>OCT251562</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4600,7 +4588,7 @@
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>OCT251227</t>
+          <t>OCT251563</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4627,7 +4615,7 @@
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>OCT251228</t>
+          <t>OCT251564</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4654,7 +4642,7 @@
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>OCT251229</t>
+          <t>OCT251565</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4681,7 +4669,7 @@
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>OCT251230</t>
+          <t>OCT251566</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4708,7 +4696,7 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>OCT251231</t>
+          <t>OCT251567</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4735,7 +4723,7 @@
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>OCT251232</t>
+          <t>OCT251568</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4762,7 +4750,7 @@
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>OCT251233</t>
+          <t>OCT251569</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4789,7 +4777,7 @@
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>OCT251234</t>
+          <t>OCT251570</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4816,7 +4804,7 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>OCT251235</t>
+          <t>OCT251571</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4843,7 +4831,7 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>OCT251236</t>
+          <t>OCT251572</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4870,7 +4858,7 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>OCT251237</t>
+          <t>OCT251573</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4897,7 +4885,7 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>OCT251238</t>
+          <t>OCT251574</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4924,7 +4912,7 @@
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>OCT251239</t>
+          <t>OCT251575</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4951,7 +4939,7 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>OCT251240</t>
+          <t>OCT251576</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4978,7 +4966,7 @@
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t>OCT251241</t>
+          <t>OCT251577</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5005,7 +4993,7 @@
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>OCT251242</t>
+          <t>OCT251578</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5032,7 +5020,7 @@
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t>OCT251243</t>
+          <t>OCT251579</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5059,7 +5047,7 @@
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t>OCT251244</t>
+          <t>OCT251580</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5086,7 +5074,7 @@
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t>OCT251245</t>
+          <t>OCT251581</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5113,7 +5101,7 @@
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t>OCT251246</t>
+          <t>OCT251582</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5140,7 +5128,7 @@
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t>OCT251247</t>
+          <t>OCT251583</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5167,7 +5155,7 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>OCT251248</t>
+          <t>OCT251584</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5194,7 +5182,7 @@
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>OCT251249</t>
+          <t>OCT251585</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5221,7 +5209,7 @@
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>OCT251250</t>
+          <t>OCT251586</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5248,7 +5236,7 @@
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t>OCT251251</t>
+          <t>OCT251587</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5275,7 +5263,7 @@
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t>OCT251252</t>
+          <t>OCT251588</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5302,7 +5290,7 @@
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t>OCT251253</t>
+          <t>OCT251589</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5329,7 +5317,7 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>OCT251254</t>
+          <t>OCT251590</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5356,7 +5344,7 @@
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t>OCT251255</t>
+          <t>OCT251591</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5383,7 +5371,7 @@
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t>OCT251256</t>
+          <t>OCT251592</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5410,7 +5398,7 @@
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t>OCT251257</t>
+          <t>OCT251593</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5437,7 +5425,7 @@
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t>OCT251258</t>
+          <t>OCT251594</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5464,7 +5452,7 @@
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t>OCT251259</t>
+          <t>OCT251595</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5491,7 +5479,7 @@
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t>OCT251260</t>
+          <t>OCT251596</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5518,7 +5506,7 @@
     <row r="189">
       <c r="B189" t="inlineStr">
         <is>
-          <t>OCT251261</t>
+          <t>OCT251597</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5545,7 +5533,7 @@
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
-          <t>OCT251262</t>
+          <t>OCT251598</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5572,7 +5560,7 @@
     <row r="191">
       <c r="B191" t="inlineStr">
         <is>
-          <t>OCT251263</t>
+          <t>OCT251599</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5599,7 +5587,7 @@
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t>OCT251264</t>
+          <t>OCT251600</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5626,7 +5614,7 @@
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t>OCT251265</t>
+          <t>OCT251601</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5653,7 +5641,7 @@
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t>OCT251266</t>
+          <t>OCT251602</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5680,7 +5668,7 @@
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t>OCT251267</t>
+          <t>OCT251603</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5707,7 +5695,7 @@
     <row r="196">
       <c r="B196" t="inlineStr">
         <is>
-          <t>OCT251268</t>
+          <t>OCT251604</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5734,7 +5722,7 @@
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
-          <t>OCT251269</t>
+          <t>OCT251605</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5761,7 +5749,7 @@
     <row r="198">
       <c r="B198" t="inlineStr">
         <is>
-          <t>OCT251270</t>
+          <t>OCT251606</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5788,7 +5776,7 @@
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t>OCT251271</t>
+          <t>OCT251607</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5815,7 +5803,7 @@
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t>OCT251272</t>
+          <t>OCT251608</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5842,7 +5830,7 @@
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t>OCT251273</t>
+          <t>OCT251609</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5869,7 +5857,7 @@
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t>OCT251274</t>
+          <t>OCT251610</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5896,7 +5884,7 @@
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t>OCT251275</t>
+          <t>OCT251611</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5923,7 +5911,7 @@
     <row r="204">
       <c r="B204" t="inlineStr">
         <is>
-          <t>OCT251276</t>
+          <t>OCT251612</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5950,7 +5938,7 @@
     <row r="205">
       <c r="B205" t="inlineStr">
         <is>
-          <t>OCT251277</t>
+          <t>OCT251613</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5977,7 +5965,7 @@
     <row r="206">
       <c r="B206" t="inlineStr">
         <is>
-          <t>OCT251278</t>
+          <t>OCT251614</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6004,7 +5992,7 @@
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
-          <t>OCT251279</t>
+          <t>OCT251615</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6031,7 +6019,7 @@
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t>OCT251280</t>
+          <t>OCT251616</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6058,7 +6046,7 @@
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t>OCT251281</t>
+          <t>OCT251617</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6085,7 +6073,7 @@
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t>OCT251282</t>
+          <t>OCT251618</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6112,7 +6100,7 @@
     <row r="211">
       <c r="B211" t="inlineStr">
         <is>
-          <t>OCT251283</t>
+          <t>OCT251619</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6139,7 +6127,7 @@
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t>OCT251284</t>
+          <t>OCT251620</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6166,7 +6154,7 @@
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t>OCT251285</t>
+          <t>OCT251621</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6193,7 +6181,7 @@
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t>OCT251286</t>
+          <t>OCT251622</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6220,7 +6208,7 @@
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t>OCT251287</t>
+          <t>OCT251623</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6247,7 +6235,7 @@
     <row r="216">
       <c r="B216" t="inlineStr">
         <is>
-          <t>OCT251288</t>
+          <t>OCT251624</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6274,7 +6262,7 @@
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
-          <t>OCT251289</t>
+          <t>OCT251625</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6301,7 +6289,7 @@
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t>OCT251290</t>
+          <t>OCT251626</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6328,7 +6316,7 @@
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t>OCT251291</t>
+          <t>OCT251627</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6355,7 +6343,7 @@
     <row r="220">
       <c r="B220" t="inlineStr">
         <is>
-          <t>OCT251292</t>
+          <t>OCT251628</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6382,7 +6370,7 @@
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t>OCT251293</t>
+          <t>OCT251629</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6409,7 +6397,7 @@
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t>OCT251294</t>
+          <t>OCT251630</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6436,7 +6424,7 @@
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t>OCT251295</t>
+          <t>OCT251631</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6463,7 +6451,7 @@
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t>OCT251296</t>
+          <t>OCT251632</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6490,7 +6478,7 @@
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>OCT251297</t>
+          <t>OCT251633</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6517,7 +6505,7 @@
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t>OCT251298</t>
+          <t>OCT251634</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6544,7 +6532,7 @@
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
-          <t>OCT251299</t>
+          <t>OCT251635</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6571,7 +6559,7 @@
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t>OCT251300</t>
+          <t>OCT251636</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6598,7 +6586,7 @@
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t>OCT251301</t>
+          <t>OCT251637</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6625,7 +6613,7 @@
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t>OCT251302</t>
+          <t>OCT251638</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6652,7 +6640,7 @@
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t>OCT251303</t>
+          <t>OCT251639</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6679,7 +6667,7 @@
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t>OCT251304</t>
+          <t>OCT251640</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6706,7 +6694,7 @@
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t>OCT251305</t>
+          <t>OCT251641</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6733,7 +6721,7 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t>OCT251306</t>
+          <t>OCT251642</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6760,7 +6748,7 @@
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t>OCT251307</t>
+          <t>OCT251643</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6787,7 +6775,7 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t>OCT251308</t>
+          <t>OCT251644</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6814,7 +6802,7 @@
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t>OCT251309</t>
+          <t>OCT251645</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6841,7 +6829,7 @@
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t>OCT251310</t>
+          <t>OCT251646</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6868,7 +6856,7 @@
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t>OCT251311</t>
+          <t>OCT251647</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6895,7 +6883,7 @@
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t>OCT251312</t>
+          <t>OCT251648</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6922,7 +6910,7 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
-          <t>OCT251313</t>
+          <t>OCT251649</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6949,7 +6937,7 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t>OCT251314</t>
+          <t>OCT251650</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6976,7 +6964,7 @@
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t>OCT251315</t>
+          <t>OCT251651</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7003,7 +6991,7 @@
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t>OCT251316</t>
+          <t>OCT251652</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7030,7 +7018,7 @@
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t>OCT251317</t>
+          <t>OCT251653</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7057,7 +7045,7 @@
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t>OCT251318</t>
+          <t>OCT251654</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7084,7 +7072,7 @@
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t>OCT251319</t>
+          <t>OCT251655</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7111,7 +7099,7 @@
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>OCT251320</t>
+          <t>OCT251656</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7138,7 +7126,7 @@
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t>OCT251321</t>
+          <t>OCT251657</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7165,7 +7153,7 @@
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t>OCT251322</t>
+          <t>OCT251658</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7192,7 +7180,7 @@
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t>OCT251323</t>
+          <t>OCT251659</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7219,7 +7207,7 @@
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t>OCT251324</t>
+          <t>OCT251660</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7246,7 +7234,7 @@
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
-          <t>OCT251325</t>
+          <t>OCT251661</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7273,7 +7261,7 @@
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
-          <t>OCT251326</t>
+          <t>OCT251662</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7300,7 +7288,7 @@
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
-          <t>OCT251327</t>
+          <t>OCT251663</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7327,7 +7315,7 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t>OCT251328</t>
+          <t>OCT251664</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7354,7 +7342,7 @@
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
-          <t>OCT251329</t>
+          <t>OCT251665</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7381,7 +7369,7 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
-          <t>OCT251330</t>
+          <t>OCT251666</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7408,7 +7396,7 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>OCT251331</t>
+          <t>OCT251667</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7435,7 +7423,7 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t>OCT251332</t>
+          <t>OCT251668</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7462,7 +7450,7 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t>OCT251333</t>
+          <t>OCT251669</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7489,7 +7477,7 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t>OCT251334</t>
+          <t>OCT251670</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7516,7 +7504,7 @@
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t>OCT251335</t>
+          <t>OCT251671</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7543,7 +7531,7 @@
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
-          <t>OCT251336</t>
+          <t>OCT251672</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7570,7 +7558,7 @@
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t>OCT251337</t>
+          <t>OCT251673</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7597,7 +7585,7 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>OCT251338</t>
+          <t>OCT251674</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7624,7 +7612,7 @@
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t>OCT251339</t>
+          <t>OCT251675</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7651,7 +7639,7 @@
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t>OCT251340</t>
+          <t>OCT251676</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7678,7 +7666,7 @@
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t>OCT251341</t>
+          <t>OCT251677</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7705,7 +7693,7 @@
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>OCT251342</t>
+          <t>OCT251678</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7732,7 +7720,7 @@
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>OCT251343</t>
+          <t>OCT251679</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7759,7 +7747,7 @@
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>OCT251344</t>
+          <t>OCT251680</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7786,7 +7774,7 @@
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>OCT251345</t>
+          <t>OCT251681</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7813,7 +7801,7 @@
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>OCT251346</t>
+          <t>OCT251682</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7840,7 +7828,7 @@
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>OCT251347</t>
+          <t>OCT251683</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7867,7 +7855,7 @@
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>OCT251348</t>
+          <t>OCT251684</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7894,7 +7882,7 @@
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>OCT251349</t>
+          <t>OCT251685</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7921,7 +7909,7 @@
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>OCT251350</t>
+          <t>OCT251686</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7948,7 +7936,7 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>OCT251351</t>
+          <t>OCT251687</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7975,7 +7963,7 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>OCT251352</t>
+          <t>OCT251688</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8002,7 +7990,7 @@
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>OCT251353</t>
+          <t>OCT251689</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8029,7 +8017,7 @@
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>OCT251354</t>
+          <t>OCT251690</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8056,7 +8044,7 @@
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>OCT251355</t>
+          <t>OCT251691</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8083,7 +8071,7 @@
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>OCT251356</t>
+          <t>OCT251692</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8110,7 +8098,7 @@
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>OCT251357</t>
+          <t>OCT251693</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8137,7 +8125,7 @@
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>OCT251358</t>
+          <t>OCT251694</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8164,7 +8152,7 @@
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
-          <t>OCT251359</t>
+          <t>OCT251695</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8191,7 +8179,7 @@
     <row r="288">
       <c r="B288" t="inlineStr">
         <is>
-          <t>OCT251360</t>
+          <t>OCT251696</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8218,7 +8206,7 @@
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>OCT251361</t>
+          <t>OCT251697</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8245,7 +8233,7 @@
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>OCT251362</t>
+          <t>OCT251698</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8272,7 +8260,7 @@
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>OCT251363</t>
+          <t>OCT251699</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8299,7 +8287,7 @@
     <row r="292">
       <c r="B292" t="inlineStr">
         <is>
-          <t>OCT251364</t>
+          <t>OCT251700</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8326,7 +8314,7 @@
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>OCT251365</t>
+          <t>OCT251701</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8353,7 +8341,7 @@
     <row r="294">
       <c r="B294" t="inlineStr">
         <is>
-          <t>OCT251366</t>
+          <t>OCT251702</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8380,7 +8368,7 @@
     <row r="295">
       <c r="B295" t="inlineStr">
         <is>
-          <t>OCT251367</t>
+          <t>OCT251703</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8407,7 +8395,7 @@
     <row r="296">
       <c r="B296" t="inlineStr">
         <is>
-          <t>OCT251368</t>
+          <t>OCT251704</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8434,7 +8422,7 @@
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
-          <t>OCT251369</t>
+          <t>OCT251705</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8461,7 +8449,7 @@
     <row r="298">
       <c r="B298" t="inlineStr">
         <is>
-          <t>OCT251370</t>
+          <t>OCT251706</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8488,7 +8476,7 @@
     <row r="299">
       <c r="B299" t="inlineStr">
         <is>
-          <t>OCT251371</t>
+          <t>OCT251707</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8515,7 +8503,7 @@
     <row r="300">
       <c r="B300" t="inlineStr">
         <is>
-          <t>OCT251372</t>
+          <t>OCT251708</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8542,7 +8530,7 @@
     <row r="301">
       <c r="B301" t="inlineStr">
         <is>
-          <t>OCT251373</t>
+          <t>OCT251709</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8569,7 +8557,7 @@
     <row r="302">
       <c r="B302" t="inlineStr">
         <is>
-          <t>OCT251374</t>
+          <t>OCT251710</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8596,7 +8584,7 @@
     <row r="303">
       <c r="B303" t="inlineStr">
         <is>
-          <t>OCT251375</t>
+          <t>OCT251711</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8623,7 +8611,7 @@
     <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>OCT251376</t>
+          <t>OCT251712</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8650,7 +8638,7 @@
     <row r="305">
       <c r="B305" t="inlineStr">
         <is>
-          <t>OCT251377</t>
+          <t>OCT251713</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8677,7 +8665,7 @@
     <row r="306">
       <c r="B306" t="inlineStr">
         <is>
-          <t>OCT251378</t>
+          <t>OCT251714</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8704,7 +8692,7 @@
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
-          <t>OCT251379</t>
+          <t>OCT251715</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8731,7 +8719,7 @@
     <row r="308">
       <c r="B308" t="inlineStr">
         <is>
-          <t>OCT251380</t>
+          <t>OCT251716</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8758,7 +8746,7 @@
     <row r="309">
       <c r="B309" t="inlineStr">
         <is>
-          <t>OCT251381</t>
+          <t>OCT251717</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8785,7 +8773,7 @@
     <row r="310">
       <c r="B310" t="inlineStr">
         <is>
-          <t>OCT251382</t>
+          <t>OCT251718</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8812,7 +8800,7 @@
     <row r="311">
       <c r="B311" t="inlineStr">
         <is>
-          <t>OCT251383</t>
+          <t>OCT251719</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8839,7 +8827,7 @@
     <row r="312">
       <c r="B312" t="inlineStr">
         <is>
-          <t>OCT251384</t>
+          <t>OCT251720</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8866,7 +8854,7 @@
     <row r="313">
       <c r="B313" t="inlineStr">
         <is>
-          <t>OCT251385</t>
+          <t>OCT251721</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8893,7 +8881,7 @@
     <row r="314">
       <c r="B314" t="inlineStr">
         <is>
-          <t>OCT251386</t>
+          <t>OCT251722</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8920,7 +8908,7 @@
     <row r="315">
       <c r="B315" t="inlineStr">
         <is>
-          <t>OCT251387</t>
+          <t>OCT251723</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8947,7 +8935,7 @@
     <row r="316">
       <c r="B316" t="inlineStr">
         <is>
-          <t>OCT251388</t>
+          <t>OCT251724</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8974,7 +8962,7 @@
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
-          <t>OCT251389</t>
+          <t>OCT251725</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9001,7 +8989,7 @@
     <row r="318">
       <c r="B318" t="inlineStr">
         <is>
-          <t>OCT251390</t>
+          <t>OCT251726</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9028,7 +9016,7 @@
     <row r="319">
       <c r="B319" t="inlineStr">
         <is>
-          <t>OCT251391</t>
+          <t>OCT251727</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9055,7 +9043,7 @@
     <row r="320">
       <c r="B320" t="inlineStr">
         <is>
-          <t>OCT251392</t>
+          <t>OCT251728</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9082,7 +9070,7 @@
     <row r="321">
       <c r="B321" t="inlineStr">
         <is>
-          <t>OCT251393</t>
+          <t>OCT251729</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9109,7 +9097,7 @@
     <row r="322">
       <c r="B322" t="inlineStr">
         <is>
-          <t>OCT251394</t>
+          <t>OCT251730</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9136,7 +9124,7 @@
     <row r="323">
       <c r="B323" t="inlineStr">
         <is>
-          <t>OCT251395</t>
+          <t>OCT251731</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9163,7 +9151,7 @@
     <row r="324">
       <c r="B324" t="inlineStr">
         <is>
-          <t>OCT251396</t>
+          <t>OCT251732</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9190,7 +9178,7 @@
     <row r="325">
       <c r="B325" t="inlineStr">
         <is>
-          <t>OCT251397</t>
+          <t>OCT251733</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9217,7 +9205,7 @@
     <row r="326">
       <c r="B326" t="inlineStr">
         <is>
-          <t>OCT251398</t>
+          <t>OCT251734</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9244,7 +9232,7 @@
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
-          <t>OCT251399</t>
+          <t>OCT251735</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9271,7 +9259,7 @@
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>OCT251400</t>
+          <t>OCT251736</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9298,7 +9286,7 @@
     <row r="329">
       <c r="B329" t="inlineStr">
         <is>
-          <t>OCT251401</t>
+          <t>OCT251737</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9325,7 +9313,7 @@
     <row r="330">
       <c r="B330" t="inlineStr">
         <is>
-          <t>OCT251402</t>
+          <t>OCT251738</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9352,7 +9340,7 @@
     <row r="331">
       <c r="B331" t="inlineStr">
         <is>
-          <t>OCT251403</t>
+          <t>OCT251739</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9379,7 +9367,7 @@
     <row r="332">
       <c r="B332" t="inlineStr">
         <is>
-          <t>OCT251404</t>
+          <t>OCT251740</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9406,7 +9394,7 @@
     <row r="333">
       <c r="B333" t="inlineStr">
         <is>
-          <t>OCT251405</t>
+          <t>OCT251741</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9433,7 +9421,7 @@
     <row r="334">
       <c r="B334" t="inlineStr">
         <is>
-          <t>OCT251406</t>
+          <t>OCT251742</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -9460,7 +9448,7 @@
     <row r="335">
       <c r="B335" t="inlineStr">
         <is>
-          <t>OCT251407</t>
+          <t>OCT251743</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -9487,7 +9475,7 @@
     <row r="336">
       <c r="B336" t="inlineStr">
         <is>
-          <t>OCT251408</t>
+          <t>OCT251744</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -9514,7 +9502,7 @@
     <row r="337">
       <c r="B337" t="inlineStr">
         <is>
-          <t>OCT251409</t>
+          <t>OCT251745</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -9541,7 +9529,7 @@
     <row r="338">
       <c r="B338" t="inlineStr">
         <is>
-          <t>OCT251410</t>
+          <t>OCT251746</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -9568,7 +9556,7 @@
     <row r="339">
       <c r="B339" t="inlineStr">
         <is>
-          <t>OCT251411</t>
+          <t>OCT251747</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9595,7 +9583,7 @@
     <row r="340">
       <c r="B340" t="inlineStr">
         <is>
-          <t>OCT251412</t>
+          <t>OCT251748</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -9622,7 +9610,7 @@
     <row r="341">
       <c r="B341" t="inlineStr">
         <is>
-          <t>OCT251413</t>
+          <t>OCT251749</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -9649,7 +9637,7 @@
     <row r="342">
       <c r="B342" t="inlineStr">
         <is>
-          <t>OCT251414</t>
+          <t>OCT251750</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -9676,7 +9664,7 @@
     <row r="343">
       <c r="B343" t="inlineStr">
         <is>
-          <t>OCT251415</t>
+          <t>OCT251751</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -9703,7 +9691,7 @@
     <row r="344">
       <c r="B344" t="inlineStr">
         <is>
-          <t>OCT251416</t>
+          <t>OCT251752</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -9730,7 +9718,7 @@
     <row r="345">
       <c r="B345" t="inlineStr">
         <is>
-          <t>OCT251417</t>
+          <t>OCT251753</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -9757,7 +9745,7 @@
     <row r="346">
       <c r="B346" t="inlineStr">
         <is>
-          <t>OCT251418</t>
+          <t>OCT251754</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -9784,7 +9772,7 @@
     <row r="347">
       <c r="B347" t="inlineStr">
         <is>
-          <t>OCT251419</t>
+          <t>OCT251755</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -9811,7 +9799,7 @@
     <row r="348">
       <c r="B348" t="inlineStr">
         <is>
-          <t>OCT251420</t>
+          <t>OCT251756</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -9838,7 +9826,7 @@
     <row r="349">
       <c r="B349" t="inlineStr">
         <is>
-          <t>OCT251421</t>
+          <t>OCT251757</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9865,7 +9853,7 @@
     <row r="350">
       <c r="B350" t="inlineStr">
         <is>
-          <t>OCT251422</t>
+          <t>OCT251758</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -9892,7 +9880,7 @@
     <row r="351">
       <c r="B351" t="inlineStr">
         <is>
-          <t>OCT251423</t>
+          <t>OCT251759</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9919,7 +9907,7 @@
     <row r="352">
       <c r="B352" t="inlineStr">
         <is>
-          <t>OCT251424</t>
+          <t>OCT251760</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9946,7 +9934,7 @@
     <row r="353">
       <c r="B353" t="inlineStr">
         <is>
-          <t>OCT251425</t>
+          <t>OCT251761</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9973,7 +9961,7 @@
     <row r="354">
       <c r="B354" t="inlineStr">
         <is>
-          <t>OCT251426</t>
+          <t>OCT251762</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10000,7 +9988,7 @@
     <row r="355">
       <c r="B355" t="inlineStr">
         <is>
-          <t>OCT251427</t>
+          <t>OCT251763</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10027,7 +10015,7 @@
     <row r="356">
       <c r="B356" t="inlineStr">
         <is>
-          <t>OCT251428</t>
+          <t>OCT251764</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10054,7 +10042,7 @@
     <row r="357">
       <c r="B357" t="inlineStr">
         <is>
-          <t>OCT251429</t>
+          <t>OCT251765</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10081,7 +10069,7 @@
     <row r="358">
       <c r="B358" t="inlineStr">
         <is>
-          <t>OCT251430</t>
+          <t>OCT251766</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10108,7 +10096,7 @@
     <row r="359">
       <c r="B359" t="inlineStr">
         <is>
-          <t>OCT251431</t>
+          <t>OCT251767</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10135,7 +10123,7 @@
     <row r="360">
       <c r="B360" t="inlineStr">
         <is>
-          <t>OCT251432</t>
+          <t>OCT251768</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10162,7 +10150,7 @@
     <row r="361">
       <c r="B361" t="inlineStr">
         <is>
-          <t>OCT251433</t>
+          <t>OCT251769</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10189,7 +10177,7 @@
     <row r="362">
       <c r="B362" t="inlineStr">
         <is>
-          <t>OCT251434</t>
+          <t>OCT251770</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10216,7 +10204,7 @@
     <row r="363">
       <c r="B363" t="inlineStr">
         <is>
-          <t>OCT251435</t>
+          <t>OCT251771</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10243,7 +10231,7 @@
     <row r="364">
       <c r="B364" t="inlineStr">
         <is>
-          <t>OCT251436</t>
+          <t>OCT251772</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10270,7 +10258,7 @@
     <row r="365">
       <c r="B365" t="inlineStr">
         <is>
-          <t>OCT251437</t>
+          <t>OCT251773</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10297,7 +10285,7 @@
     <row r="366">
       <c r="B366" t="inlineStr">
         <is>
-          <t>OCT251438</t>
+          <t>OCT251774</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10324,7 +10312,7 @@
     <row r="367">
       <c r="B367" t="inlineStr">
         <is>
-          <t>OCT251439</t>
+          <t>OCT251775</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10351,7 +10339,7 @@
     <row r="368">
       <c r="B368" t="inlineStr">
         <is>
-          <t>OCT251440</t>
+          <t>OCT251776</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10378,7 +10366,7 @@
     <row r="369">
       <c r="B369" t="inlineStr">
         <is>
-          <t>OCT251441</t>
+          <t>OCT251777</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10405,7 +10393,7 @@
     <row r="370">
       <c r="B370" t="inlineStr">
         <is>
-          <t>OCT251442</t>
+          <t>OCT251778</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10432,7 +10420,7 @@
     <row r="371">
       <c r="B371" t="inlineStr">
         <is>
-          <t>OCT251443</t>
+          <t>OCT251779</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10459,7 +10447,7 @@
     <row r="372">
       <c r="B372" t="inlineStr">
         <is>
-          <t>OCT251444</t>
+          <t>OCT251780</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10484,7 +10472,7 @@
     <row r="373">
       <c r="B373" t="inlineStr">
         <is>
-          <t>OCT251445</t>
+          <t>OCT251781</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10511,7 +10499,7 @@
     <row r="374">
       <c r="B374" t="inlineStr">
         <is>
-          <t>OCT251446</t>
+          <t>OCT251782</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10538,7 +10526,7 @@
     <row r="375">
       <c r="B375" t="inlineStr">
         <is>
-          <t>OCT251447</t>
+          <t>OCT251783</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10565,7 +10553,7 @@
     <row r="376">
       <c r="B376" t="inlineStr">
         <is>
-          <t>OCT251448</t>
+          <t>OCT251784</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10592,7 +10580,7 @@
     <row r="377">
       <c r="B377" t="inlineStr">
         <is>
-          <t>OCT251449</t>
+          <t>OCT251785</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10617,7 +10605,7 @@
     <row r="378">
       <c r="B378" t="inlineStr">
         <is>
-          <t>OCT251450</t>
+          <t>OCT251786</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -10644,7 +10632,7 @@
     <row r="379">
       <c r="B379" t="inlineStr">
         <is>
-          <t>OCT251451</t>
+          <t>OCT251787</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10671,7 +10659,7 @@
     <row r="380">
       <c r="B380" t="inlineStr">
         <is>
-          <t>OCT251452</t>
+          <t>OCT251788</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10698,7 +10686,7 @@
     <row r="381">
       <c r="B381" t="inlineStr">
         <is>
-          <t>OCT251453</t>
+          <t>OCT251789</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10723,7 +10711,7 @@
     <row r="382">
       <c r="B382" t="inlineStr">
         <is>
-          <t>OCT251454</t>
+          <t>OCT251790</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10748,7 +10736,7 @@
     <row r="383">
       <c r="B383" t="inlineStr">
         <is>
-          <t>OCT251455</t>
+          <t>OCT251791</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10775,7 +10763,7 @@
     <row r="384">
       <c r="B384" t="inlineStr">
         <is>
-          <t>OCT251456</t>
+          <t>OCT251792</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10802,7 +10790,7 @@
     <row r="385">
       <c r="B385" t="inlineStr">
         <is>
-          <t>OCT251457</t>
+          <t>OCT251793</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10829,7 +10817,7 @@
     <row r="386">
       <c r="B386" t="inlineStr">
         <is>
-          <t>OCT251458</t>
+          <t>OCT251794</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10854,7 +10842,7 @@
     <row r="387">
       <c r="B387" t="inlineStr">
         <is>
-          <t>OCT251459</t>
+          <t>OCT251795</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -10879,7 +10867,7 @@
     <row r="388">
       <c r="B388" t="inlineStr">
         <is>
-          <t>OCT251460</t>
+          <t>OCT251796</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10906,7 +10894,7 @@
     <row r="389">
       <c r="B389" t="inlineStr">
         <is>
-          <t>OCT251461</t>
+          <t>OCT251797</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10933,7 +10921,7 @@
     <row r="390">
       <c r="B390" t="inlineStr">
         <is>
-          <t>OCT251462</t>
+          <t>OCT251798</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10960,7 +10948,7 @@
     <row r="391">
       <c r="B391" t="inlineStr">
         <is>
-          <t>OCT251463</t>
+          <t>OCT251799</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -10987,7 +10975,7 @@
     <row r="392">
       <c r="B392" t="inlineStr">
         <is>
-          <t>OCT251464</t>
+          <t>OCT251800</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11012,7 +11000,7 @@
     <row r="393">
       <c r="B393" t="inlineStr">
         <is>
-          <t>OCT251465</t>
+          <t>OCT251801</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11039,7 +11027,7 @@
     <row r="394">
       <c r="B394" t="inlineStr">
         <is>
-          <t>OCT251466</t>
+          <t>OCT251802</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11066,7 +11054,7 @@
     <row r="395">
       <c r="B395" t="inlineStr">
         <is>
-          <t>OCT251467</t>
+          <t>OCT251803</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11093,7 +11081,7 @@
     <row r="396">
       <c r="B396" t="inlineStr">
         <is>
-          <t>OCT251468</t>
+          <t>OCT251804</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11120,7 +11108,7 @@
     <row r="397">
       <c r="B397" t="inlineStr">
         <is>
-          <t>OCT251469</t>
+          <t>OCT251805</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11147,7 +11135,7 @@
     <row r="398">
       <c r="B398" t="inlineStr">
         <is>
-          <t>OCT251470</t>
+          <t>OCT251806</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11174,7 +11162,7 @@
     <row r="399">
       <c r="B399" t="inlineStr">
         <is>
-          <t>OCT251471</t>
+          <t>OCT251807</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11201,7 +11189,7 @@
     <row r="400">
       <c r="B400" t="inlineStr">
         <is>
-          <t>OCT251472</t>
+          <t>OCT251808</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11228,7 +11216,7 @@
     <row r="401">
       <c r="B401" t="inlineStr">
         <is>
-          <t>OCT251473</t>
+          <t>OCT251809</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11253,7 +11241,7 @@
     <row r="402">
       <c r="B402" t="inlineStr">
         <is>
-          <t>OCT251474</t>
+          <t>OCT251810</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11280,7 +11268,7 @@
     <row r="403">
       <c r="B403" t="inlineStr">
         <is>
-          <t>OCT251475</t>
+          <t>OCT251811</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -11307,7 +11295,7 @@
     <row r="404">
       <c r="B404" t="inlineStr">
         <is>
-          <t>OCT251476</t>
+          <t>OCT251812</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -11334,7 +11322,7 @@
     <row r="405">
       <c r="B405" t="inlineStr">
         <is>
-          <t>OCT251477</t>
+          <t>OCT251813</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -11361,7 +11349,7 @@
     <row r="406">
       <c r="B406" t="inlineStr">
         <is>
-          <t>OCT251478</t>
+          <t>OCT251814</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -11388,7 +11376,7 @@
     <row r="407">
       <c r="B407" t="inlineStr">
         <is>
-          <t>OCT251479</t>
+          <t>OCT251815</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11415,7 +11403,7 @@
     <row r="408">
       <c r="B408" t="inlineStr">
         <is>
-          <t>OCT251480</t>
+          <t>OCT251816</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -11442,7 +11430,7 @@
     <row r="409">
       <c r="B409" t="inlineStr">
         <is>
-          <t>OCT251481</t>
+          <t>OCT251817</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11467,7 +11455,7 @@
     <row r="410">
       <c r="B410" t="inlineStr">
         <is>
-          <t>OCT251482</t>
+          <t>OCT251818</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -11494,7 +11482,7 @@
     <row r="411">
       <c r="B411" t="inlineStr">
         <is>
-          <t>OCT251483</t>
+          <t>OCT251819</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -11521,7 +11509,7 @@
     <row r="412">
       <c r="B412" t="inlineStr">
         <is>
-          <t>OCT251484</t>
+          <t>OCT251820</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11548,7 +11536,7 @@
     <row r="413">
       <c r="B413" t="inlineStr">
         <is>
-          <t>OCT251485</t>
+          <t>OCT251821</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -11575,7 +11563,7 @@
     <row r="414">
       <c r="B414" t="inlineStr">
         <is>
-          <t>OCT251486</t>
+          <t>OCT251822</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -11602,7 +11590,7 @@
     <row r="415">
       <c r="B415" t="inlineStr">
         <is>
-          <t>OCT251487</t>
+          <t>OCT251823</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -11629,7 +11617,7 @@
     <row r="416">
       <c r="B416" t="inlineStr">
         <is>
-          <t>OCT251488</t>
+          <t>OCT251824</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -11656,7 +11644,7 @@
     <row r="417">
       <c r="B417" t="inlineStr">
         <is>
-          <t>OCT251489</t>
+          <t>OCT251825</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11681,7 +11669,7 @@
     <row r="418">
       <c r="B418" t="inlineStr">
         <is>
-          <t>OCT251490</t>
+          <t>OCT251826</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11708,7 +11696,7 @@
     <row r="419">
       <c r="B419" t="inlineStr">
         <is>
-          <t>OCT251491</t>
+          <t>OCT251827</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -11733,7 +11721,7 @@
     <row r="420">
       <c r="B420" t="inlineStr">
         <is>
-          <t>OCT251492</t>
+          <t>OCT251828</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11760,7 +11748,7 @@
     <row r="421">
       <c r="B421" t="inlineStr">
         <is>
-          <t>OCT251493</t>
+          <t>OCT251829</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11785,7 +11773,7 @@
     <row r="422">
       <c r="B422" t="inlineStr">
         <is>
-          <t>OCT251494</t>
+          <t>OCT251830</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11810,7 +11798,7 @@
     <row r="423">
       <c r="B423" t="inlineStr">
         <is>
-          <t>OCT251495</t>
+          <t>OCT251831</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11837,7 +11825,7 @@
     <row r="424">
       <c r="B424" t="inlineStr">
         <is>
-          <t>OCT251496</t>
+          <t>OCT251832</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11864,7 +11852,7 @@
     <row r="425">
       <c r="B425" t="inlineStr">
         <is>
-          <t>OCT251497</t>
+          <t>OCT251833</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11891,7 +11879,7 @@
     <row r="426">
       <c r="B426" t="inlineStr">
         <is>
-          <t>OCT251498</t>
+          <t>OCT251834</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11918,7 +11906,7 @@
     <row r="427">
       <c r="B427" t="inlineStr">
         <is>
-          <t>OCT251499</t>
+          <t>OCT251835</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11945,7 +11933,7 @@
     <row r="428">
       <c r="B428" t="inlineStr">
         <is>
-          <t>OCT251500</t>
+          <t>OCT251836</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11972,7 +11960,7 @@
     <row r="429">
       <c r="B429" t="inlineStr">
         <is>
-          <t>OCT251501</t>
+          <t>OCT251837</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -11997,7 +11985,7 @@
     <row r="430">
       <c r="B430" t="inlineStr">
         <is>
-          <t>OCT251502</t>
+          <t>OCT251838</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12024,7 +12012,7 @@
     <row r="431">
       <c r="B431" t="inlineStr">
         <is>
-          <t>OCT251503</t>
+          <t>OCT251839</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12051,7 +12039,7 @@
     <row r="432">
       <c r="B432" t="inlineStr">
         <is>
-          <t>OCT251504</t>
+          <t>OCT251840</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12078,7 +12066,7 @@
     <row r="433">
       <c r="B433" t="inlineStr">
         <is>
-          <t>OCT251505</t>
+          <t>OCT251841</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12105,7 +12093,7 @@
     <row r="434">
       <c r="B434" t="inlineStr">
         <is>
-          <t>OCT251506</t>
+          <t>OCT251842</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12132,7 +12120,7 @@
     <row r="435">
       <c r="B435" t="inlineStr">
         <is>
-          <t>OCT251507</t>
+          <t>OCT251843</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12159,7 +12147,7 @@
     <row r="436">
       <c r="B436" t="inlineStr">
         <is>
-          <t>OCT251508</t>
+          <t>OCT251844</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12186,7 +12174,7 @@
     <row r="437">
       <c r="B437" t="inlineStr">
         <is>
-          <t>OCT251509</t>
+          <t>OCT251845</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -12213,7 +12201,7 @@
     <row r="438">
       <c r="B438" t="inlineStr">
         <is>
-          <t>OCT251510</t>
+          <t>OCT251846</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12240,7 +12228,7 @@
     <row r="439">
       <c r="B439" t="inlineStr">
         <is>
-          <t>OCT251511</t>
+          <t>OCT251847</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12267,7 +12255,7 @@
     <row r="440">
       <c r="B440" t="inlineStr">
         <is>
-          <t>OCT251512</t>
+          <t>OCT251848</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -12294,7 +12282,7 @@
     <row r="441">
       <c r="B441" t="inlineStr">
         <is>
-          <t>OCT251513</t>
+          <t>OCT251849</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -12321,7 +12309,7 @@
     <row r="442">
       <c r="B442" t="inlineStr">
         <is>
-          <t>OCT251514</t>
+          <t>OCT251850</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -12346,7 +12334,7 @@
     <row r="443">
       <c r="B443" t="inlineStr">
         <is>
-          <t>OCT251515</t>
+          <t>OCT251851</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -12373,7 +12361,7 @@
     <row r="444">
       <c r="B444" t="inlineStr">
         <is>
-          <t>OCT251516</t>
+          <t>OCT251852</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12400,7 +12388,7 @@
     <row r="445">
       <c r="B445" t="inlineStr">
         <is>
-          <t>OCT251517</t>
+          <t>OCT251853</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -12427,7 +12415,7 @@
     <row r="446">
       <c r="B446" t="inlineStr">
         <is>
-          <t>OCT251518</t>
+          <t>OCT251854</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -12454,7 +12442,7 @@
     <row r="447">
       <c r="B447" t="inlineStr">
         <is>
-          <t>OCT251519</t>
+          <t>OCT251855</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12481,7 +12469,7 @@
     <row r="448">
       <c r="B448" t="inlineStr">
         <is>
-          <t>OCT251520</t>
+          <t>OCT251856</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -12508,7 +12496,7 @@
     <row r="449">
       <c r="B449" t="inlineStr">
         <is>
-          <t>OCT251521</t>
+          <t>OCT251857</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -12535,7 +12523,7 @@
     <row r="450">
       <c r="B450" t="inlineStr">
         <is>
-          <t>OCT251522</t>
+          <t>OCT251858</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -12562,7 +12550,7 @@
     <row r="451">
       <c r="B451" t="inlineStr">
         <is>
-          <t>OCT251523</t>
+          <t>OCT251859</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12589,7 +12577,7 @@
     <row r="452">
       <c r="B452" t="inlineStr">
         <is>
-          <t>OCT251524</t>
+          <t>OCT251860</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -12614,7 +12602,7 @@
     <row r="453">
       <c r="B453" t="inlineStr">
         <is>
-          <t>OCT251525</t>
+          <t>OCT251861</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -12639,7 +12627,7 @@
     <row r="454">
       <c r="B454" t="inlineStr">
         <is>
-          <t>OCT251526</t>
+          <t>OCT251862</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -12664,7 +12652,7 @@
     <row r="455">
       <c r="B455" t="inlineStr">
         <is>
-          <t>OCT251527</t>
+          <t>OCT251863</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -12691,7 +12679,7 @@
     <row r="456">
       <c r="B456" t="inlineStr">
         <is>
-          <t>OCT251528</t>
+          <t>OCT251864</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -12718,7 +12706,7 @@
     <row r="457">
       <c r="B457" t="inlineStr">
         <is>
-          <t>OCT251529</t>
+          <t>OCT251865</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -12745,7 +12733,7 @@
     <row r="458">
       <c r="B458" t="inlineStr">
         <is>
-          <t>OCT251530</t>
+          <t>OCT251866</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -12772,7 +12760,7 @@
     <row r="459">
       <c r="B459" t="inlineStr">
         <is>
-          <t>OCT251531</t>
+          <t>OCT251867</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -12799,7 +12787,7 @@
     <row r="460">
       <c r="B460" t="inlineStr">
         <is>
-          <t>OCT251532</t>
+          <t>OCT251868</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12826,7 +12814,7 @@
     <row r="461">
       <c r="B461" t="inlineStr">
         <is>
-          <t>OCT251533</t>
+          <t>OCT251869</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12853,7 +12841,7 @@
     <row r="462">
       <c r="B462" t="inlineStr">
         <is>
-          <t>OCT251534</t>
+          <t>OCT251870</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12880,7 +12868,7 @@
     <row r="463">
       <c r="B463" t="inlineStr">
         <is>
-          <t>OCT251535</t>
+          <t>OCT251871</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12907,7 +12895,7 @@
     <row r="464">
       <c r="B464" t="inlineStr">
         <is>
-          <t>OCT251536</t>
+          <t>OCT251872</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12934,7 +12922,7 @@
     <row r="465">
       <c r="B465" t="inlineStr">
         <is>
-          <t>OCT251537</t>
+          <t>OCT251873</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12961,7 +12949,7 @@
     <row r="466">
       <c r="B466" t="inlineStr">
         <is>
-          <t>OCT251538</t>
+          <t>OCT251874</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -12988,7 +12976,7 @@
     <row r="467">
       <c r="B467" t="inlineStr">
         <is>
-          <t>OCT251539</t>
+          <t>OCT251875</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -13015,7 +13003,7 @@
     <row r="468">
       <c r="B468" t="inlineStr">
         <is>
-          <t>OCT251540</t>
+          <t>OCT251876</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13042,7 +13030,7 @@
     <row r="469">
       <c r="B469" t="inlineStr">
         <is>
-          <t>OCT251541</t>
+          <t>OCT251877</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13069,7 +13057,7 @@
     <row r="470">
       <c r="B470" t="inlineStr">
         <is>
-          <t>OCT251542</t>
+          <t>OCT251878</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -13096,7 +13084,7 @@
     <row r="471">
       <c r="B471" t="inlineStr">
         <is>
-          <t>OCT251543</t>
+          <t>OCT251879</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13123,7 +13111,7 @@
     <row r="472">
       <c r="B472" t="inlineStr">
         <is>
-          <t>OCT251544</t>
+          <t>OCT251880</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -13150,7 +13138,7 @@
     <row r="473">
       <c r="B473" t="inlineStr">
         <is>
-          <t>OCT251545</t>
+          <t>OCT251881</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13177,7 +13165,7 @@
     <row r="474">
       <c r="B474" t="inlineStr">
         <is>
-          <t>OCT251546</t>
+          <t>OCT251882</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -13204,7 +13192,7 @@
     <row r="475">
       <c r="B475" t="inlineStr">
         <is>
-          <t>OCT251547</t>
+          <t>OCT251883</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13231,7 +13219,7 @@
     <row r="476">
       <c r="B476" t="inlineStr">
         <is>
-          <t>OCT251548</t>
+          <t>OCT251884</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -13258,7 +13246,7 @@
     <row r="477">
       <c r="B477" t="inlineStr">
         <is>
-          <t>OCT251549</t>
+          <t>OCT251885</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -13285,7 +13273,7 @@
     <row r="478">
       <c r="B478" t="inlineStr">
         <is>
-          <t>OCT251550</t>
+          <t>OCT251886</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -13312,7 +13300,7 @@
     <row r="479">
       <c r="B479" t="inlineStr">
         <is>
-          <t>OCT251551</t>
+          <t>OCT251887</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -13339,7 +13327,7 @@
     <row r="480">
       <c r="B480" t="inlineStr">
         <is>
-          <t>OCT251552</t>
+          <t>OCT251888</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -13366,7 +13354,7 @@
     <row r="481">
       <c r="B481" t="inlineStr">
         <is>
-          <t>OCT251553</t>
+          <t>OCT251889</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -13393,7 +13381,7 @@
     <row r="482">
       <c r="B482" t="inlineStr">
         <is>
-          <t>OCT251554</t>
+          <t>OCT251890</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -13420,7 +13408,7 @@
     <row r="483">
       <c r="B483" t="inlineStr">
         <is>
-          <t>OCT251555</t>
+          <t>OCT251891</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13447,7 +13435,7 @@
     <row r="484">
       <c r="B484" t="inlineStr">
         <is>
-          <t>OCT251556</t>
+          <t>OCT251892</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -13472,7 +13460,7 @@
     <row r="485">
       <c r="B485" t="inlineStr">
         <is>
-          <t>OCT251557</t>
+          <t>OCT251893</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -13497,7 +13485,7 @@
     <row r="486">
       <c r="B486" t="inlineStr">
         <is>
-          <t>OCT251558</t>
+          <t>OCT251894</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -13524,7 +13512,7 @@
     <row r="487">
       <c r="B487" t="inlineStr">
         <is>
-          <t>OCT251559</t>
+          <t>OCT251895</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -13551,7 +13539,7 @@
     <row r="488">
       <c r="B488" t="inlineStr">
         <is>
-          <t>OCT251560</t>
+          <t>OCT251896</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -13578,7 +13566,7 @@
     <row r="489">
       <c r="B489" t="inlineStr">
         <is>
-          <t>OCT251561</t>
+          <t>OCT251897</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -13605,7 +13593,7 @@
     <row r="490">
       <c r="B490" t="inlineStr">
         <is>
-          <t>OCT251562</t>
+          <t>OCT251898</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -13632,7 +13620,7 @@
     <row r="491">
       <c r="B491" t="inlineStr">
         <is>
-          <t>OCT251563</t>
+          <t>OCT251899</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -13659,7 +13647,7 @@
     <row r="492">
       <c r="B492" t="inlineStr">
         <is>
-          <t>OCT251564</t>
+          <t>OCT251900</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13686,7 +13674,7 @@
     <row r="493">
       <c r="B493" t="inlineStr">
         <is>
-          <t>OCT251565</t>
+          <t>OCT251901</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13713,7 +13701,7 @@
     <row r="494">
       <c r="B494" t="inlineStr">
         <is>
-          <t>OCT251566</t>
+          <t>OCT251902</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13740,7 +13728,7 @@
     <row r="495">
       <c r="B495" t="inlineStr">
         <is>
-          <t>OCT251567</t>
+          <t>OCT251903</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13767,7 +13755,7 @@
     <row r="496">
       <c r="B496" t="inlineStr">
         <is>
-          <t>OCT251568</t>
+          <t>OCT251904</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13794,7 +13782,7 @@
     <row r="497">
       <c r="B497" t="inlineStr">
         <is>
-          <t>OCT251569</t>
+          <t>OCT251905</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13821,7 +13809,7 @@
     <row r="498">
       <c r="B498" t="inlineStr">
         <is>
-          <t>OCT251570</t>
+          <t>OCT251906</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13848,7 +13836,7 @@
     <row r="499">
       <c r="B499" t="inlineStr">
         <is>
-          <t>OCT251571</t>
+          <t>OCT251907</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13875,7 +13863,7 @@
     <row r="500">
       <c r="B500" t="inlineStr">
         <is>
-          <t>OCT251572</t>
+          <t>OCT251908</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13902,7 +13890,7 @@
     <row r="501">
       <c r="B501" t="inlineStr">
         <is>
-          <t>OCT251573</t>
+          <t>OCT251909</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -13929,7 +13917,7 @@
     <row r="502">
       <c r="B502" t="inlineStr">
         <is>
-          <t>OCT251574</t>
+          <t>OCT251910</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -13956,7 +13944,7 @@
     <row r="503">
       <c r="B503" t="inlineStr">
         <is>
-          <t>OCT251575</t>
+          <t>OCT251911</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -13983,7 +13971,7 @@
     <row r="504">
       <c r="B504" t="inlineStr">
         <is>
-          <t>OCT251576</t>
+          <t>OCT251912</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -14010,7 +13998,7 @@
     <row r="505">
       <c r="B505" t="inlineStr">
         <is>
-          <t>OCT251577</t>
+          <t>OCT251913</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -14037,7 +14025,7 @@
     <row r="506">
       <c r="B506" t="inlineStr">
         <is>
-          <t>OCT251578</t>
+          <t>OCT251914</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -14064,7 +14052,7 @@
     <row r="507">
       <c r="B507" t="inlineStr">
         <is>
-          <t>OCT251579</t>
+          <t>OCT251915</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -14091,7 +14079,7 @@
     <row r="508">
       <c r="B508" t="inlineStr">
         <is>
-          <t>OCT251580</t>
+          <t>OCT251916</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -14118,7 +14106,7 @@
     <row r="509">
       <c r="B509" t="inlineStr">
         <is>
-          <t>OCT251581</t>
+          <t>OCT251917</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14145,7 +14133,7 @@
     <row r="510">
       <c r="B510" t="inlineStr">
         <is>
-          <t>OCT251582</t>
+          <t>OCT251918</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14172,7 +14160,7 @@
     <row r="511">
       <c r="B511" t="inlineStr">
         <is>
-          <t>OCT251583</t>
+          <t>OCT251919</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14199,7 +14187,7 @@
     <row r="512">
       <c r="B512" t="inlineStr">
         <is>
-          <t>OCT251584</t>
+          <t>OCT251920</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14226,7 +14214,7 @@
     <row r="513">
       <c r="B513" t="inlineStr">
         <is>
-          <t>OCT251585</t>
+          <t>OCT251921</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14253,7 +14241,7 @@
     <row r="514">
       <c r="B514" t="inlineStr">
         <is>
-          <t>OCT251586</t>
+          <t>OCT251922</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -14280,7 +14268,7 @@
     <row r="515">
       <c r="B515" t="inlineStr">
         <is>
-          <t>OCT251587</t>
+          <t>OCT251923</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -14307,7 +14295,7 @@
     <row r="516">
       <c r="B516" t="inlineStr">
         <is>
-          <t>OCT251588</t>
+          <t>OCT251924</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -14334,7 +14322,7 @@
     <row r="517">
       <c r="B517" t="inlineStr">
         <is>
-          <t>OCT251589</t>
+          <t>OCT251925</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -14361,7 +14349,7 @@
     <row r="518">
       <c r="B518" t="inlineStr">
         <is>
-          <t>OCT251590</t>
+          <t>OCT251926</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -14388,7 +14376,7 @@
     <row r="519">
       <c r="B519" t="inlineStr">
         <is>
-          <t>OCT251591</t>
+          <t>OCT251927</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -14415,7 +14403,7 @@
     <row r="520">
       <c r="B520" t="inlineStr">
         <is>
-          <t>OCT251592</t>
+          <t>OCT251928</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -14442,7 +14430,7 @@
     <row r="521">
       <c r="B521" t="inlineStr">
         <is>
-          <t>OCT251593</t>
+          <t>OCT251929</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -14469,7 +14457,7 @@
     <row r="522">
       <c r="B522" t="inlineStr">
         <is>
-          <t>OCT251594</t>
+          <t>OCT251930</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -14496,7 +14484,7 @@
     <row r="523">
       <c r="B523" t="inlineStr">
         <is>
-          <t>OCT251595</t>
+          <t>OCT251931</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -14523,7 +14511,7 @@
     <row r="524">
       <c r="B524" t="inlineStr">
         <is>
-          <t>OCT251596</t>
+          <t>OCT251932</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -14550,7 +14538,7 @@
     <row r="525">
       <c r="B525" t="inlineStr">
         <is>
-          <t>OCT251597</t>
+          <t>OCT251933</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -14577,7 +14565,7 @@
     <row r="526">
       <c r="B526" t="inlineStr">
         <is>
-          <t>OCT251598</t>
+          <t>OCT251934</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -14604,7 +14592,7 @@
     <row r="527">
       <c r="B527" t="inlineStr">
         <is>
-          <t>OCT251599</t>
+          <t>OCT251935</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -14631,7 +14619,7 @@
     <row r="528">
       <c r="B528" t="inlineStr">
         <is>
-          <t>OCT251600</t>
+          <t>OCT251936</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -14658,7 +14646,7 @@
     <row r="529">
       <c r="B529" t="inlineStr">
         <is>
-          <t>OCT251601</t>
+          <t>OCT251937</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -14685,7 +14673,7 @@
     <row r="530">
       <c r="B530" t="inlineStr">
         <is>
-          <t>OCT251602</t>
+          <t>OCT251938</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -14712,7 +14700,7 @@
     <row r="531">
       <c r="B531" t="inlineStr">
         <is>
-          <t>OCT251603</t>
+          <t>OCT251939</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -14739,7 +14727,7 @@
     <row r="532">
       <c r="B532" t="inlineStr">
         <is>
-          <t>OCT251604</t>
+          <t>OCT251940</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -14766,7 +14754,7 @@
     <row r="533">
       <c r="B533" t="inlineStr">
         <is>
-          <t>OCT251605</t>
+          <t>OCT251941</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -14793,7 +14781,7 @@
     <row r="534">
       <c r="B534" t="inlineStr">
         <is>
-          <t>OCT251606</t>
+          <t>OCT251942</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -14820,7 +14808,7 @@
     <row r="535">
       <c r="B535" t="inlineStr">
         <is>
-          <t>OCT251607</t>
+          <t>OCT251943</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -14847,7 +14835,7 @@
     <row r="536">
       <c r="B536" t="inlineStr">
         <is>
-          <t>OCT251608</t>
+          <t>OCT251944</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -14874,7 +14862,7 @@
     <row r="537">
       <c r="B537" t="inlineStr">
         <is>
-          <t>OCT251609</t>
+          <t>OCT251945</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -14901,7 +14889,7 @@
     <row r="538">
       <c r="B538" t="inlineStr">
         <is>
-          <t>OCT251610</t>
+          <t>OCT251946</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14928,7 +14916,7 @@
     <row r="539">
       <c r="B539" t="inlineStr">
         <is>
-          <t>OCT251611</t>
+          <t>OCT251947</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -14955,7 +14943,7 @@
     <row r="540">
       <c r="B540" t="inlineStr">
         <is>
-          <t>OCT251612</t>
+          <t>OCT251948</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -14982,7 +14970,7 @@
     <row r="541">
       <c r="B541" t="inlineStr">
         <is>
-          <t>OCT251613</t>
+          <t>OCT251949</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -15009,7 +14997,7 @@
     <row r="542">
       <c r="B542" t="inlineStr">
         <is>
-          <t>OCT251614</t>
+          <t>OCT251950</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -15036,7 +15024,7 @@
     <row r="543">
       <c r="B543" t="inlineStr">
         <is>
-          <t>OCT251615</t>
+          <t>OCT251951</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -15063,7 +15051,7 @@
     <row r="544">
       <c r="B544" t="inlineStr">
         <is>
-          <t>OCT251616</t>
+          <t>OCT251952</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15090,7 +15078,7 @@
     <row r="545">
       <c r="B545" t="inlineStr">
         <is>
-          <t>OCT251617</t>
+          <t>OCT251953</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -15117,7 +15105,7 @@
     <row r="546">
       <c r="B546" t="inlineStr">
         <is>
-          <t>OCT251618</t>
+          <t>OCT251954</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -15144,7 +15132,7 @@
     <row r="547">
       <c r="B547" t="inlineStr">
         <is>
-          <t>OCT251619</t>
+          <t>OCT251955</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -15171,7 +15159,7 @@
     <row r="548">
       <c r="B548" t="inlineStr">
         <is>
-          <t>OCT251620</t>
+          <t>OCT251956</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -15198,7 +15186,7 @@
     <row r="549">
       <c r="B549" t="inlineStr">
         <is>
-          <t>OCT251621</t>
+          <t>OCT251957</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -15225,7 +15213,7 @@
     <row r="550">
       <c r="B550" t="inlineStr">
         <is>
-          <t>OCT251622</t>
+          <t>OCT251958</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -15252,7 +15240,7 @@
     <row r="551">
       <c r="B551" t="inlineStr">
         <is>
-          <t>OCT251623</t>
+          <t>OCT251959</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15279,7 +15267,7 @@
     <row r="552">
       <c r="B552" t="inlineStr">
         <is>
-          <t>OCT251624</t>
+          <t>OCT251960</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -15306,7 +15294,7 @@
     <row r="553">
       <c r="B553" t="inlineStr">
         <is>
-          <t>OCT251625</t>
+          <t>OCT251961</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15333,7 +15321,7 @@
     <row r="554">
       <c r="B554" t="inlineStr">
         <is>
-          <t>OCT251626</t>
+          <t>OCT251962</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -15360,7 +15348,7 @@
     <row r="555">
       <c r="B555" t="inlineStr">
         <is>
-          <t>OCT251627</t>
+          <t>OCT251963</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -15387,7 +15375,7 @@
     <row r="556">
       <c r="B556" t="inlineStr">
         <is>
-          <t>OCT251628</t>
+          <t>OCT251964</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -15414,7 +15402,7 @@
     <row r="557">
       <c r="B557" t="inlineStr">
         <is>
-          <t>OCT251629</t>
+          <t>OCT251965</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -15441,7 +15429,7 @@
     <row r="558">
       <c r="B558" t="inlineStr">
         <is>
-          <t>OCT251630</t>
+          <t>OCT251966</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -15468,7 +15456,7 @@
     <row r="559">
       <c r="B559" t="inlineStr">
         <is>
-          <t>OCT251631</t>
+          <t>OCT251967</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -15495,7 +15483,7 @@
     <row r="560">
       <c r="B560" t="inlineStr">
         <is>
-          <t>OCT251632</t>
+          <t>OCT251968</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -15522,7 +15510,7 @@
     <row r="561">
       <c r="B561" t="inlineStr">
         <is>
-          <t>OCT251633</t>
+          <t>OCT251969</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -15549,7 +15537,7 @@
     <row r="562">
       <c r="B562" t="inlineStr">
         <is>
-          <t>OCT251634</t>
+          <t>OCT251970</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -15576,7 +15564,7 @@
     <row r="563">
       <c r="B563" t="inlineStr">
         <is>
-          <t>OCT251635</t>
+          <t>OCT251971</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -15603,7 +15591,7 @@
     <row r="564">
       <c r="B564" t="inlineStr">
         <is>
-          <t>OCT251636</t>
+          <t>OCT251972</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -15630,7 +15618,7 @@
     <row r="565">
       <c r="B565" t="inlineStr">
         <is>
-          <t>OCT251637</t>
+          <t>OCT251973</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -15657,7 +15645,7 @@
     <row r="566">
       <c r="B566" t="inlineStr">
         <is>
-          <t>OCT251638</t>
+          <t>OCT251974</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -15684,7 +15672,7 @@
     <row r="567">
       <c r="B567" t="inlineStr">
         <is>
-          <t>OCT251639</t>
+          <t>OCT251975</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -15711,7 +15699,7 @@
     <row r="568">
       <c r="B568" t="inlineStr">
         <is>
-          <t>OCT251640</t>
+          <t>OCT251976</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -15738,7 +15726,7 @@
     <row r="569">
       <c r="B569" t="inlineStr">
         <is>
-          <t>OCT251641</t>
+          <t>OCT251977</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -15765,7 +15753,7 @@
     <row r="570">
       <c r="B570" t="inlineStr">
         <is>
-          <t>OCT251642</t>
+          <t>OCT251978</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -15792,7 +15780,7 @@
     <row r="571">
       <c r="B571" t="inlineStr">
         <is>
-          <t>OCT251643</t>
+          <t>OCT251979</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -15819,7 +15807,7 @@
     <row r="572">
       <c r="B572" t="inlineStr">
         <is>
-          <t>OCT251644</t>
+          <t>OCT251980</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -15846,7 +15834,7 @@
     <row r="573">
       <c r="B573" t="inlineStr">
         <is>
-          <t>OCT251645</t>
+          <t>OCT251981</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15873,7 +15861,7 @@
     <row r="574">
       <c r="B574" t="inlineStr">
         <is>
-          <t>OCT251646</t>
+          <t>OCT251982</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -15900,7 +15888,7 @@
     <row r="575">
       <c r="B575" t="inlineStr">
         <is>
-          <t>OCT251647</t>
+          <t>OCT251983</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -15927,7 +15915,7 @@
     <row r="576">
       <c r="B576" t="inlineStr">
         <is>
-          <t>OCT251648</t>
+          <t>OCT251984</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -15954,7 +15942,7 @@
     <row r="577">
       <c r="B577" t="inlineStr">
         <is>
-          <t>OCT251649</t>
+          <t>OCT251985</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -15981,7 +15969,7 @@
     <row r="578">
       <c r="B578" t="inlineStr">
         <is>
-          <t>OCT251650</t>
+          <t>OCT251986</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -16008,7 +15996,7 @@
     <row r="579">
       <c r="B579" t="inlineStr">
         <is>
-          <t>OCT251651</t>
+          <t>OCT251987</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -16033,7 +16021,7 @@
     <row r="580">
       <c r="B580" t="inlineStr">
         <is>
-          <t>OCT251652</t>
+          <t>OCT251988</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -16058,7 +16046,7 @@
     <row r="581">
       <c r="B581" t="inlineStr">
         <is>
-          <t>OCT251653</t>
+          <t>OCT251989</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -16085,7 +16073,7 @@
     <row r="582">
       <c r="B582" t="inlineStr">
         <is>
-          <t>OCT251654</t>
+          <t>OCT251990</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16112,7 +16100,7 @@
     <row r="583">
       <c r="B583" t="inlineStr">
         <is>
-          <t>OCT251655</t>
+          <t>OCT251991</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16139,7 +16127,7 @@
     <row r="584">
       <c r="B584" t="inlineStr">
         <is>
-          <t>OCT251656</t>
+          <t>OCT251992</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -16166,7 +16154,7 @@
     <row r="585">
       <c r="B585" t="inlineStr">
         <is>
-          <t>OCT251657</t>
+          <t>OCT251993</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -16193,7 +16181,7 @@
     <row r="586">
       <c r="B586" t="inlineStr">
         <is>
-          <t>OCT251658</t>
+          <t>OCT251994</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -16220,7 +16208,7 @@
     <row r="587">
       <c r="B587" t="inlineStr">
         <is>
-          <t>OCT251659</t>
+          <t>OCT251995</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -16247,7 +16235,7 @@
     <row r="588">
       <c r="B588" t="inlineStr">
         <is>
-          <t>OCT251660</t>
+          <t>OCT251996</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -16274,7 +16262,7 @@
     <row r="589">
       <c r="B589" t="inlineStr">
         <is>
-          <t>OCT251661</t>
+          <t>OCT251997</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -16301,7 +16289,7 @@
     <row r="590">
       <c r="B590" t="inlineStr">
         <is>
-          <t>OCT251662</t>
+          <t>OCT251998</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -16328,7 +16316,7 @@
     <row r="591">
       <c r="B591" t="inlineStr">
         <is>
-          <t>OCT251663</t>
+          <t>OCT251999</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -16355,7 +16343,7 @@
     <row r="592">
       <c r="B592" t="inlineStr">
         <is>
-          <t>OCT251664</t>
+          <t>OCT252000</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -16382,7 +16370,7 @@
     <row r="593">
       <c r="B593" t="inlineStr">
         <is>
-          <t>OCT251665</t>
+          <t>OCT252001</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -16407,7 +16395,7 @@
     <row r="594">
       <c r="B594" t="inlineStr">
         <is>
-          <t>OCT251666</t>
+          <t>OCT252002</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -16434,7 +16422,7 @@
     <row r="595">
       <c r="B595" t="inlineStr">
         <is>
-          <t>OCT251667</t>
+          <t>OCT252003</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -16459,7 +16447,7 @@
     <row r="596">
       <c r="B596" t="inlineStr">
         <is>
-          <t>OCT251668</t>
+          <t>OCT252004</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -16486,7 +16474,7 @@
     <row r="597">
       <c r="B597" t="inlineStr">
         <is>
-          <t>OCT251669</t>
+          <t>OCT252005</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -16511,7 +16499,7 @@
     <row r="598">
       <c r="B598" t="inlineStr">
         <is>
-          <t>OCT251670</t>
+          <t>OCT252006</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -16538,7 +16526,7 @@
     <row r="599">
       <c r="B599" t="inlineStr">
         <is>
-          <t>OCT251671</t>
+          <t>OCT252007</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -16565,7 +16553,7 @@
     <row r="600">
       <c r="B600" t="inlineStr">
         <is>
-          <t>OCT251672</t>
+          <t>OCT252008</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -16592,7 +16580,7 @@
     <row r="601">
       <c r="B601" t="inlineStr">
         <is>
-          <t>OCT251673</t>
+          <t>OCT252009</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -16617,7 +16605,7 @@
     <row r="602">
       <c r="B602" t="inlineStr">
         <is>
-          <t>OCT251674</t>
+          <t>OCT252010</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -16642,7 +16630,7 @@
     <row r="603">
       <c r="B603" t="inlineStr">
         <is>
-          <t>OCT251675</t>
+          <t>OCT252011</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -16667,7 +16655,7 @@
     <row r="604">
       <c r="B604" t="inlineStr">
         <is>
-          <t>OCT251676</t>
+          <t>OCT252012</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -16692,7 +16680,7 @@
     <row r="605">
       <c r="B605" t="inlineStr">
         <is>
-          <t>OCT251677</t>
+          <t>OCT252013</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -16717,7 +16705,7 @@
     <row r="606">
       <c r="B606" t="inlineStr">
         <is>
-          <t>OCT251678</t>
+          <t>OCT252014</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -16742,7 +16730,7 @@
     <row r="607">
       <c r="B607" t="inlineStr">
         <is>
-          <t>OCT251679</t>
+          <t>OCT252015</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -16767,7 +16755,7 @@
     <row r="608">
       <c r="B608" t="inlineStr">
         <is>
-          <t>OCT251680</t>
+          <t>OCT252016</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -16792,7 +16780,7 @@
     <row r="609">
       <c r="B609" t="inlineStr">
         <is>
-          <t>OCT251681</t>
+          <t>OCT252017</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -16817,7 +16805,7 @@
     <row r="610">
       <c r="B610" t="inlineStr">
         <is>
-          <t>OCT251682</t>
+          <t>OCT252018</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -16844,7 +16832,7 @@
     <row r="611">
       <c r="B611" t="inlineStr">
         <is>
-          <t>OCT251683</t>
+          <t>OCT252019</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -16869,7 +16857,7 @@
     <row r="612">
       <c r="B612" t="inlineStr">
         <is>
-          <t>OCT251684</t>
+          <t>OCT252020</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -16896,7 +16884,7 @@
     <row r="613">
       <c r="B613" t="inlineStr">
         <is>
-          <t>OCT251685</t>
+          <t>OCT252021</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16923,7 +16911,7 @@
     <row r="614">
       <c r="B614" t="inlineStr">
         <is>
-          <t>OCT251686</t>
+          <t>OCT252022</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -16950,7 +16938,7 @@
     <row r="615">
       <c r="B615" t="inlineStr">
         <is>
-          <t>OCT251687</t>
+          <t>OCT252023</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -16977,7 +16965,7 @@
     <row r="616">
       <c r="B616" t="inlineStr">
         <is>
-          <t>OCT251688</t>
+          <t>OCT252024</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -17002,7 +16990,7 @@
     <row r="617">
       <c r="B617" t="inlineStr">
         <is>
-          <t>OCT251689</t>
+          <t>OCT252025</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -17029,7 +17017,7 @@
     <row r="618">
       <c r="B618" t="inlineStr">
         <is>
-          <t>OCT251690</t>
+          <t>OCT252026</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17056,7 +17044,7 @@
     <row r="619">
       <c r="B619" t="inlineStr">
         <is>
-          <t>OCT251691</t>
+          <t>OCT252027</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -17083,7 +17071,7 @@
     <row r="620">
       <c r="B620" t="inlineStr">
         <is>
-          <t>OCT251692</t>
+          <t>OCT252028</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -17108,7 +17096,7 @@
     <row r="621">
       <c r="B621" t="inlineStr">
         <is>
-          <t>OCT251693</t>
+          <t>OCT252029</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -17133,7 +17121,7 @@
     <row r="622">
       <c r="B622" t="inlineStr">
         <is>
-          <t>OCT251694</t>
+          <t>OCT252030</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -17158,7 +17146,7 @@
     <row r="623">
       <c r="B623" t="inlineStr">
         <is>
-          <t>OCT251695</t>
+          <t>OCT252031</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17183,7 +17171,7 @@
     <row r="624">
       <c r="B624" t="inlineStr">
         <is>
-          <t>OCT251696</t>
+          <t>OCT252032</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -17208,7 +17196,7 @@
     <row r="625">
       <c r="B625" t="inlineStr">
         <is>
-          <t>OCT251697</t>
+          <t>OCT252033</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -17233,7 +17221,7 @@
     <row r="626">
       <c r="B626" t="inlineStr">
         <is>
-          <t>OCT251698</t>
+          <t>OCT252034</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -17258,7 +17246,7 @@
     <row r="627">
       <c r="B627" t="inlineStr">
         <is>
-          <t>OCT251699</t>
+          <t>OCT252035</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -17283,7 +17271,7 @@
     <row r="628">
       <c r="B628" t="inlineStr">
         <is>
-          <t>OCT251700</t>
+          <t>OCT252036</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -17308,7 +17296,7 @@
     <row r="629">
       <c r="B629" t="inlineStr">
         <is>
-          <t>OCT251701</t>
+          <t>OCT252037</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -17333,7 +17321,7 @@
     <row r="630">
       <c r="B630" t="inlineStr">
         <is>
-          <t>OCT251702</t>
+          <t>OCT252038</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -17358,7 +17346,7 @@
     <row r="631">
       <c r="B631" t="inlineStr">
         <is>
-          <t>OCT251703</t>
+          <t>OCT252039</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -17383,7 +17371,7 @@
     <row r="632">
       <c r="B632" t="inlineStr">
         <is>
-          <t>OCT251704</t>
+          <t>OCT252040</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -17410,7 +17398,7 @@
     <row r="633">
       <c r="B633" t="inlineStr">
         <is>
-          <t>OCT251705</t>
+          <t>OCT252041</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -17437,7 +17425,7 @@
     <row r="634">
       <c r="B634" t="inlineStr">
         <is>
-          <t>OCT251706</t>
+          <t>OCT252042</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -17464,7 +17452,7 @@
     <row r="635">
       <c r="B635" t="inlineStr">
         <is>
-          <t>OCT251707</t>
+          <t>OCT252043</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -17491,7 +17479,7 @@
     <row r="636">
       <c r="B636" t="inlineStr">
         <is>
-          <t>OCT251708</t>
+          <t>OCT252044</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -17518,7 +17506,7 @@
     <row r="637">
       <c r="B637" t="inlineStr">
         <is>
-          <t>OCT251709</t>
+          <t>OCT252045</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -17545,7 +17533,7 @@
     <row r="638">
       <c r="B638" t="inlineStr">
         <is>
-          <t>OCT251710</t>
+          <t>OCT252046</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -17572,7 +17560,7 @@
     <row r="639">
       <c r="B639" t="inlineStr">
         <is>
-          <t>OCT251711</t>
+          <t>OCT252047</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -17599,7 +17587,7 @@
     <row r="640">
       <c r="B640" t="inlineStr">
         <is>
-          <t>OCT251712</t>
+          <t>OCT252048</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -17626,7 +17614,7 @@
     <row r="641">
       <c r="B641" t="inlineStr">
         <is>
-          <t>OCT251713</t>
+          <t>OCT252049</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -17653,7 +17641,7 @@
     <row r="642">
       <c r="B642" t="inlineStr">
         <is>
-          <t>OCT251714</t>
+          <t>OCT252050</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -17678,7 +17666,7 @@
     <row r="643">
       <c r="B643" t="inlineStr">
         <is>
-          <t>OCT251715</t>
+          <t>OCT252051</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -17705,7 +17693,7 @@
     <row r="644">
       <c r="B644" t="inlineStr">
         <is>
-          <t>OCT251716</t>
+          <t>OCT252052</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -17732,7 +17720,7 @@
     <row r="645">
       <c r="B645" t="inlineStr">
         <is>
-          <t>OCT251717</t>
+          <t>OCT252053</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -17759,7 +17747,7 @@
     <row r="646">
       <c r="B646" t="inlineStr">
         <is>
-          <t>OCT251718</t>
+          <t>OCT252054</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -17786,7 +17774,7 @@
     <row r="647">
       <c r="B647" t="inlineStr">
         <is>
-          <t>OCT251719</t>
+          <t>OCT252055</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -17813,7 +17801,7 @@
     <row r="648">
       <c r="B648" t="inlineStr">
         <is>
-          <t>OCT251720</t>
+          <t>OCT252056</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -17840,7 +17828,7 @@
     <row r="649">
       <c r="B649" t="inlineStr">
         <is>
-          <t>OCT251721</t>
+          <t>OCT252057</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -17865,7 +17853,7 @@
     <row r="650">
       <c r="B650" t="inlineStr">
         <is>
-          <t>OCT251722</t>
+          <t>OCT252058</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -17892,7 +17880,7 @@
     <row r="651">
       <c r="B651" t="inlineStr">
         <is>
-          <t>OCT251723</t>
+          <t>OCT252059</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -17919,7 +17907,7 @@
     <row r="652">
       <c r="B652" t="inlineStr">
         <is>
-          <t>OCT251724</t>
+          <t>OCT252060</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -17944,7 +17932,7 @@
     <row r="653">
       <c r="B653" t="inlineStr">
         <is>
-          <t>OCT251725</t>
+          <t>OCT252061</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -17969,7 +17957,7 @@
     <row r="654">
       <c r="B654" t="inlineStr">
         <is>
-          <t>OCT251726</t>
+          <t>OCT252062</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -17994,7 +17982,7 @@
     <row r="655">
       <c r="B655" t="inlineStr">
         <is>
-          <t>OCT251727</t>
+          <t>OCT252063</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -18019,7 +18007,7 @@
     <row r="656">
       <c r="B656" t="inlineStr">
         <is>
-          <t>OCT251728</t>
+          <t>OCT252064</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -18044,7 +18032,7 @@
     <row r="657">
       <c r="B657" t="inlineStr">
         <is>
-          <t>OCT251729</t>
+          <t>OCT252065</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18069,7 +18057,7 @@
     <row r="658">
       <c r="B658" t="inlineStr">
         <is>
-          <t>OCT251730</t>
+          <t>OCT252066</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -18096,7 +18084,7 @@
     <row r="659">
       <c r="B659" t="inlineStr">
         <is>
-          <t>OCT251731</t>
+          <t>OCT252067</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18123,7 +18111,7 @@
     <row r="660">
       <c r="B660" t="inlineStr">
         <is>
-          <t>OCT251732</t>
+          <t>OCT252068</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -18150,7 +18138,7 @@
     <row r="661">
       <c r="B661" t="inlineStr">
         <is>
-          <t>OCT251733</t>
+          <t>OCT252069</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18177,7 +18165,7 @@
     <row r="662">
       <c r="B662" t="inlineStr">
         <is>
-          <t>OCT251734</t>
+          <t>OCT252070</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18204,7 +18192,7 @@
     <row r="663">
       <c r="B663" t="inlineStr">
         <is>
-          <t>OCT251735</t>
+          <t>OCT252071</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18231,7 +18219,7 @@
     <row r="664">
       <c r="B664" t="inlineStr">
         <is>
-          <t>OCT251736</t>
+          <t>OCT252072</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -18256,7 +18244,7 @@
     <row r="665">
       <c r="B665" t="inlineStr">
         <is>
-          <t>OCT251737</t>
+          <t>OCT252073</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18283,7 +18271,7 @@
     <row r="666">
       <c r="B666" t="inlineStr">
         <is>
-          <t>OCT251738</t>
+          <t>OCT252074</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18308,7 +18296,7 @@
     <row r="667">
       <c r="B667" t="inlineStr">
         <is>
-          <t>OCT251739</t>
+          <t>OCT252075</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18335,7 +18323,7 @@
     <row r="668">
       <c r="B668" t="inlineStr">
         <is>
-          <t>OCT251740</t>
+          <t>OCT252076</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -18360,7 +18348,7 @@
     <row r="669">
       <c r="B669" t="inlineStr">
         <is>
-          <t>OCT251741</t>
+          <t>OCT252077</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18385,7 +18373,7 @@
     <row r="670">
       <c r="B670" t="inlineStr">
         <is>
-          <t>OCT251742</t>
+          <t>OCT252078</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -18410,7 +18398,7 @@
     <row r="671">
       <c r="B671" t="inlineStr">
         <is>
-          <t>OCT251743</t>
+          <t>OCT252079</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18437,7 +18425,7 @@
     <row r="672">
       <c r="B672" t="inlineStr">
         <is>
-          <t>OCT251744</t>
+          <t>OCT252080</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -18464,7 +18452,7 @@
     <row r="673">
       <c r="B673" t="inlineStr">
         <is>
-          <t>OCT251745</t>
+          <t>OCT252081</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -18491,7 +18479,7 @@
     <row r="674">
       <c r="B674" t="inlineStr">
         <is>
-          <t>OCT251746</t>
+          <t>OCT252082</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -18518,7 +18506,7 @@
     <row r="675">
       <c r="B675" t="inlineStr">
         <is>
-          <t>OCT251747</t>
+          <t>OCT252083</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -18543,7 +18531,7 @@
     <row r="676">
       <c r="B676" t="inlineStr">
         <is>
-          <t>OCT251748</t>
+          <t>OCT252084</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -18570,7 +18558,7 @@
     <row r="677">
       <c r="B677" t="inlineStr">
         <is>
-          <t>OCT251749</t>
+          <t>OCT252085</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -18597,7 +18585,7 @@
     <row r="678">
       <c r="B678" t="inlineStr">
         <is>
-          <t>OCT251750</t>
+          <t>OCT252086</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -18624,7 +18612,7 @@
     <row r="679">
       <c r="B679" t="inlineStr">
         <is>
-          <t>OCT251751</t>
+          <t>OCT252087</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -18649,7 +18637,7 @@
     <row r="680">
       <c r="B680" t="inlineStr">
         <is>
-          <t>OCT251752</t>
+          <t>OCT252088</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -18674,7 +18662,7 @@
     <row r="681">
       <c r="B681" t="inlineStr">
         <is>
-          <t>OCT251753</t>
+          <t>OCT252089</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -18699,7 +18687,7 @@
     <row r="682">
       <c r="B682" t="inlineStr">
         <is>
-          <t>OCT251754</t>
+          <t>OCT252090</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -18724,7 +18712,7 @@
     <row r="683">
       <c r="B683" t="inlineStr">
         <is>
-          <t>OCT251755</t>
+          <t>OCT252091</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -18751,7 +18739,7 @@
     <row r="684">
       <c r="B684" t="inlineStr">
         <is>
-          <t>OCT251756</t>
+          <t>OCT252092</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -18776,7 +18764,7 @@
     <row r="685">
       <c r="B685" t="inlineStr">
         <is>
-          <t>OCT251757</t>
+          <t>OCT252093</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -18803,7 +18791,7 @@
     <row r="686">
       <c r="B686" t="inlineStr">
         <is>
-          <t>OCT251758</t>
+          <t>OCT252094</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -18830,7 +18818,7 @@
     <row r="687">
       <c r="B687" t="inlineStr">
         <is>
-          <t>OCT251759</t>
+          <t>OCT252095</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -18857,7 +18845,7 @@
     <row r="688">
       <c r="B688" t="inlineStr">
         <is>
-          <t>OCT251760</t>
+          <t>OCT252096</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -18882,7 +18870,7 @@
     <row r="689">
       <c r="B689" t="inlineStr">
         <is>
-          <t>OCT251761</t>
+          <t>OCT252097</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -18909,7 +18897,7 @@
     <row r="690">
       <c r="B690" t="inlineStr">
         <is>
-          <t>OCT251762</t>
+          <t>OCT252098</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -18936,7 +18924,7 @@
     <row r="691">
       <c r="B691" t="inlineStr">
         <is>
-          <t>OCT251763</t>
+          <t>OCT252099</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -18963,7 +18951,7 @@
     <row r="692">
       <c r="B692" t="inlineStr">
         <is>
-          <t>OCT251764</t>
+          <t>OCT252100</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -18990,7 +18978,7 @@
     <row r="693">
       <c r="B693" t="inlineStr">
         <is>
-          <t>OCT251765</t>
+          <t>OCT252101</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -19015,7 +19003,7 @@
     <row r="694">
       <c r="B694" t="inlineStr">
         <is>
-          <t>OCT251766</t>
+          <t>OCT252102</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -19042,7 +19030,7 @@
     <row r="695">
       <c r="B695" t="inlineStr">
         <is>
-          <t>OCT251767</t>
+          <t>OCT252103</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19069,7 +19057,7 @@
     <row r="696">
       <c r="B696" t="inlineStr">
         <is>
-          <t>OCT251768</t>
+          <t>OCT252104</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -19096,7 +19084,7 @@
     <row r="697">
       <c r="B697" t="inlineStr">
         <is>
-          <t>OCT251769</t>
+          <t>OCT252105</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -19123,7 +19111,7 @@
     <row r="698">
       <c r="B698" t="inlineStr">
         <is>
-          <t>OCT251770</t>
+          <t>OCT252106</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19150,7 +19138,7 @@
     <row r="699">
       <c r="B699" t="inlineStr">
         <is>
-          <t>OCT251771</t>
+          <t>OCT252107</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19175,7 +19163,7 @@
     <row r="700">
       <c r="B700" t="inlineStr">
         <is>
-          <t>OCT251772</t>
+          <t>OCT252108</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -19200,7 +19188,7 @@
     <row r="701">
       <c r="B701" t="inlineStr">
         <is>
-          <t>OCT251773</t>
+          <t>OCT252109</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -19227,7 +19215,7 @@
     <row r="702">
       <c r="B702" t="inlineStr">
         <is>
-          <t>OCT251774</t>
+          <t>OCT252110</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -19254,7 +19242,7 @@
     <row r="703">
       <c r="B703" t="inlineStr">
         <is>
-          <t>OCT251775</t>
+          <t>OCT252111</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -19281,7 +19269,7 @@
     <row r="704">
       <c r="B704" t="inlineStr">
         <is>
-          <t>OCT251776</t>
+          <t>OCT252112</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -19306,7 +19294,7 @@
     <row r="705">
       <c r="B705" t="inlineStr">
         <is>
-          <t>OCT251777</t>
+          <t>OCT252113</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -19333,7 +19321,7 @@
     <row r="706">
       <c r="B706" t="inlineStr">
         <is>
-          <t>OCT251778</t>
+          <t>OCT252114</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -19360,7 +19348,7 @@
     <row r="707">
       <c r="B707" t="inlineStr">
         <is>
-          <t>OCT251779</t>
+          <t>OCT252115</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -19385,7 +19373,7 @@
     <row r="708">
       <c r="B708" t="inlineStr">
         <is>
-          <t>OCT251780</t>
+          <t>OCT252116</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -19412,7 +19400,7 @@
     <row r="709">
       <c r="B709" t="inlineStr">
         <is>
-          <t>OCT251781</t>
+          <t>OCT252117</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -19437,7 +19425,7 @@
     <row r="710">
       <c r="B710" t="inlineStr">
         <is>
-          <t>OCT251782</t>
+          <t>OCT252118</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -19464,7 +19452,7 @@
     <row r="711">
       <c r="B711" t="inlineStr">
         <is>
-          <t>OCT251783</t>
+          <t>OCT252119</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -19491,7 +19479,7 @@
     <row r="712">
       <c r="B712" t="inlineStr">
         <is>
-          <t>OCT251784</t>
+          <t>OCT252120</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -19518,7 +19506,7 @@
     <row r="713">
       <c r="B713" t="inlineStr">
         <is>
-          <t>OCT251785</t>
+          <t>OCT252121</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -19545,7 +19533,7 @@
     <row r="714">
       <c r="B714" t="inlineStr">
         <is>
-          <t>OCT251786</t>
+          <t>OCT252122</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -19572,7 +19560,7 @@
     <row r="715">
       <c r="B715" t="inlineStr">
         <is>
-          <t>OCT251787</t>
+          <t>OCT252123</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -19599,7 +19587,7 @@
     <row r="716">
       <c r="B716" t="inlineStr">
         <is>
-          <t>OCT251788</t>
+          <t>OCT252124</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -19624,7 +19612,7 @@
     <row r="717">
       <c r="B717" t="inlineStr">
         <is>
-          <t>OCT251789</t>
+          <t>OCT252125</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -19651,7 +19639,7 @@
     <row r="718">
       <c r="B718" t="inlineStr">
         <is>
-          <t>OCT251790</t>
+          <t>OCT252126</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -19678,7 +19666,7 @@
     <row r="719">
       <c r="B719" t="inlineStr">
         <is>
-          <t>OCT251791</t>
+          <t>OCT252127</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -19705,7 +19693,7 @@
     <row r="720">
       <c r="B720" t="inlineStr">
         <is>
-          <t>OCT251792</t>
+          <t>OCT252128</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -19732,7 +19720,7 @@
     <row r="721">
       <c r="B721" t="inlineStr">
         <is>
-          <t>OCT251793</t>
+          <t>OCT252129</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -19759,7 +19747,7 @@
     <row r="722">
       <c r="B722" t="inlineStr">
         <is>
-          <t>OCT251794</t>
+          <t>OCT252130</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -19786,7 +19774,7 @@
     <row r="723">
       <c r="B723" t="inlineStr">
         <is>
-          <t>OCT251795</t>
+          <t>OCT252131</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -19813,7 +19801,7 @@
     <row r="724">
       <c r="B724" t="inlineStr">
         <is>
-          <t>OCT251796</t>
+          <t>OCT252132</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -19838,7 +19826,7 @@
     <row r="725">
       <c r="B725" t="inlineStr">
         <is>
-          <t>OCT251797</t>
+          <t>OCT252133</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -19865,7 +19853,7 @@
     <row r="726">
       <c r="B726" t="inlineStr">
         <is>
-          <t>OCT251798</t>
+          <t>OCT252134</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -19892,7 +19880,7 @@
     <row r="727">
       <c r="B727" t="inlineStr">
         <is>
-          <t>OCT251799</t>
+          <t>OCT252135</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -19919,7 +19907,7 @@
     <row r="728">
       <c r="B728" t="inlineStr">
         <is>
-          <t>OCT251800</t>
+          <t>OCT252136</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -19946,7 +19934,7 @@
     <row r="729">
       <c r="B729" t="inlineStr">
         <is>
-          <t>OCT251801</t>
+          <t>OCT252137</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -19973,7 +19961,7 @@
     <row r="730">
       <c r="B730" t="inlineStr">
         <is>
-          <t>OCT251802</t>
+          <t>OCT252138</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -20000,7 +19988,7 @@
     <row r="731">
       <c r="B731" t="inlineStr">
         <is>
-          <t>OCT251803</t>
+          <t>OCT252139</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -20027,7 +20015,7 @@
     <row r="732">
       <c r="B732" t="inlineStr">
         <is>
-          <t>OCT251804</t>
+          <t>OCT252140</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -20054,7 +20042,7 @@
     <row r="733">
       <c r="B733" t="inlineStr">
         <is>
-          <t>OCT251805</t>
+          <t>OCT252141</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -20081,7 +20069,7 @@
     <row r="734">
       <c r="B734" t="inlineStr">
         <is>
-          <t>OCT251806</t>
+          <t>OCT252142</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -20108,7 +20096,7 @@
     <row r="735">
       <c r="B735" t="inlineStr">
         <is>
-          <t>OCT251807</t>
+          <t>OCT252143</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -20135,7 +20123,7 @@
     <row r="736">
       <c r="B736" t="inlineStr">
         <is>
-          <t>OCT251808</t>
+          <t>OCT252144</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -20160,7 +20148,7 @@
     <row r="737">
       <c r="B737" t="inlineStr">
         <is>
-          <t>OCT251809</t>
+          <t>OCT252145</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20187,7 +20175,7 @@
     <row r="738">
       <c r="B738" t="inlineStr">
         <is>
-          <t>OCT251810</t>
+          <t>OCT252146</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -20214,7 +20202,7 @@
     <row r="739">
       <c r="B739" t="inlineStr">
         <is>
-          <t>OCT251811</t>
+          <t>OCT252147</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -20241,7 +20229,7 @@
     <row r="740">
       <c r="B740" t="inlineStr">
         <is>
-          <t>OCT251812</t>
+          <t>OCT252148</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -20268,7 +20256,7 @@
     <row r="741">
       <c r="B741" t="inlineStr">
         <is>
-          <t>OCT251813</t>
+          <t>OCT252149</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -20295,7 +20283,7 @@
     <row r="742">
       <c r="B742" t="inlineStr">
         <is>
-          <t>OCT251814</t>
+          <t>OCT252150</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -20322,7 +20310,7 @@
     <row r="743">
       <c r="B743" t="inlineStr">
         <is>
-          <t>OCT251815</t>
+          <t>OCT252151</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20349,7 +20337,7 @@
     <row r="744">
       <c r="B744" t="inlineStr">
         <is>
-          <t>OCT251816</t>
+          <t>OCT252152</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -20376,7 +20364,7 @@
     <row r="745">
       <c r="B745" t="inlineStr">
         <is>
-          <t>OCT251817</t>
+          <t>OCT252153</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -20403,7 +20391,7 @@
     <row r="746">
       <c r="B746" t="inlineStr">
         <is>
-          <t>OCT251818</t>
+          <t>OCT252154</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -20428,7 +20416,7 @@
     <row r="747">
       <c r="B747" t="inlineStr">
         <is>
-          <t>OCT251819</t>
+          <t>OCT252155</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -20453,7 +20441,7 @@
     <row r="748">
       <c r="B748" t="inlineStr">
         <is>
-          <t>OCT251820</t>
+          <t>OCT252156</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -20480,7 +20468,7 @@
     <row r="749">
       <c r="B749" t="inlineStr">
         <is>
-          <t>OCT251821</t>
+          <t>OCT252157</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -20505,7 +20493,7 @@
     <row r="750">
       <c r="B750" t="inlineStr">
         <is>
-          <t>OCT251822</t>
+          <t>OCT252158</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -20532,7 +20520,7 @@
     <row r="751">
       <c r="B751" t="inlineStr">
         <is>
-          <t>OCT251823</t>
+          <t>OCT252159</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -20559,7 +20547,7 @@
     <row r="752">
       <c r="B752" t="inlineStr">
         <is>
-          <t>OCT251824</t>
+          <t>OCT252160</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -20586,7 +20574,7 @@
     <row r="753">
       <c r="B753" t="inlineStr">
         <is>
-          <t>OCT251825</t>
+          <t>OCT252161</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -20613,7 +20601,7 @@
     <row r="754">
       <c r="B754" t="inlineStr">
         <is>
-          <t>OCT251826</t>
+          <t>OCT252162</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -20640,7 +20628,7 @@
     <row r="755">
       <c r="B755" t="inlineStr">
         <is>
-          <t>OCT251827</t>
+          <t>OCT252163</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -20665,7 +20653,7 @@
     <row r="756">
       <c r="B756" t="inlineStr">
         <is>
-          <t>OCT251828</t>
+          <t>OCT252164</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -20692,7 +20680,7 @@
     <row r="757">
       <c r="B757" t="inlineStr">
         <is>
-          <t>OCT251829</t>
+          <t>OCT252165</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -20717,7 +20705,7 @@
     <row r="758">
       <c r="B758" t="inlineStr">
         <is>
-          <t>OCT251830</t>
+          <t>OCT252166</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -20744,7 +20732,7 @@
     <row r="759">
       <c r="B759" t="inlineStr">
         <is>
-          <t>OCT251831</t>
+          <t>OCT252167</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -20771,7 +20759,7 @@
     <row r="760">
       <c r="B760" t="inlineStr">
         <is>
-          <t>OCT251832</t>
+          <t>OCT252168</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -20798,7 +20786,7 @@
     <row r="761">
       <c r="B761" t="inlineStr">
         <is>
-          <t>OCT251833</t>
+          <t>OCT252169</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -20825,7 +20813,7 @@
     <row r="762">
       <c r="B762" t="inlineStr">
         <is>
-          <t>OCT251834</t>
+          <t>OCT252170</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -20852,7 +20840,7 @@
     <row r="763">
       <c r="B763" t="inlineStr">
         <is>
-          <t>OCT251835</t>
+          <t>OCT252171</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -20879,7 +20867,7 @@
     <row r="764">
       <c r="B764" t="inlineStr">
         <is>
-          <t>OCT251836</t>
+          <t>OCT252172</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -20904,7 +20892,7 @@
     <row r="765">
       <c r="B765" t="inlineStr">
         <is>
-          <t>OCT251837</t>
+          <t>OCT252173</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -20931,7 +20919,7 @@
     <row r="766">
       <c r="B766" t="inlineStr">
         <is>
-          <t>OCT251838</t>
+          <t>OCT252174</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -20958,7 +20946,7 @@
     <row r="767">
       <c r="B767" t="inlineStr">
         <is>
-          <t>OCT251839</t>
+          <t>OCT252175</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -20983,7 +20971,7 @@
     <row r="768">
       <c r="B768" t="inlineStr">
         <is>
-          <t>OCT251840</t>
+          <t>OCT252176</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -21010,7 +20998,7 @@
     <row r="769">
       <c r="B769" t="inlineStr">
         <is>
-          <t>OCT251841</t>
+          <t>OCT252177</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -21035,7 +21023,7 @@
     <row r="770">
       <c r="B770" t="inlineStr">
         <is>
-          <t>OCT251842</t>
+          <t>OCT252178</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -21062,7 +21050,7 @@
     <row r="771">
       <c r="B771" t="inlineStr">
         <is>
-          <t>OCT251843</t>
+          <t>OCT252179</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -21089,7 +21077,7 @@
     <row r="772">
       <c r="B772" t="inlineStr">
         <is>
-          <t>OCT251844</t>
+          <t>OCT252180</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -21116,7 +21104,7 @@
     <row r="773">
       <c r="B773" t="inlineStr">
         <is>
-          <t>OCT251845</t>
+          <t>OCT252181</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -21143,7 +21131,7 @@
     <row r="774">
       <c r="B774" t="inlineStr">
         <is>
-          <t>OCT251846</t>
+          <t>OCT252182</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -21170,7 +21158,7 @@
     <row r="775">
       <c r="B775" t="inlineStr">
         <is>
-          <t>OCT251847</t>
+          <t>OCT252183</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -21197,7 +21185,7 @@
     <row r="776">
       <c r="B776" t="inlineStr">
         <is>
-          <t>OCT251848</t>
+          <t>OCT252184</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -21224,7 +21212,7 @@
     <row r="777">
       <c r="B777" t="inlineStr">
         <is>
-          <t>OCT251849</t>
+          <t>OCT252185</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -21249,7 +21237,7 @@
     <row r="778">
       <c r="B778" t="inlineStr">
         <is>
-          <t>OCT251850</t>
+          <t>OCT252186</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -21274,7 +21262,7 @@
     <row r="779">
       <c r="B779" t="inlineStr">
         <is>
-          <t>OCT251851</t>
+          <t>OCT252187</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -21299,7 +21287,7 @@
     <row r="780">
       <c r="B780" t="inlineStr">
         <is>
-          <t>OCT251852</t>
+          <t>OCT252188</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -21326,7 +21314,7 @@
     <row r="781">
       <c r="B781" t="inlineStr">
         <is>
-          <t>OCT251853</t>
+          <t>OCT252189</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -21351,7 +21339,7 @@
     <row r="782">
       <c r="B782" t="inlineStr">
         <is>
-          <t>OCT251854</t>
+          <t>OCT252190</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -21376,7 +21364,7 @@
     <row r="783">
       <c r="B783" t="inlineStr">
         <is>
-          <t>OCT251855</t>
+          <t>OCT252191</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -21403,7 +21391,7 @@
     <row r="784">
       <c r="B784" t="inlineStr">
         <is>
-          <t>OCT251856</t>
+          <t>OCT252192</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -21428,7 +21416,7 @@
     <row r="785">
       <c r="B785" t="inlineStr">
         <is>
-          <t>OCT251857</t>
+          <t>OCT252193</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -21453,7 +21441,7 @@
     <row r="786">
       <c r="B786" t="inlineStr">
         <is>
-          <t>OCT251858</t>
+          <t>OCT252194</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -21478,7 +21466,7 @@
     <row r="787">
       <c r="B787" t="inlineStr">
         <is>
-          <t>OCT251859</t>
+          <t>OCT252195</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -21503,7 +21491,7 @@
     <row r="788">
       <c r="B788" t="inlineStr">
         <is>
-          <t>OCT251860</t>
+          <t>OCT252196</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -21530,7 +21518,7 @@
     <row r="789">
       <c r="B789" t="inlineStr">
         <is>
-          <t>OCT251861</t>
+          <t>OCT252197</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -21557,7 +21545,7 @@
     <row r="790">
       <c r="B790" t="inlineStr">
         <is>
-          <t>OCT251862</t>
+          <t>OCT252198</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -21584,7 +21572,7 @@
     <row r="791">
       <c r="B791" t="inlineStr">
         <is>
-          <t>OCT251863</t>
+          <t>OCT252199</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -21609,7 +21597,7 @@
     <row r="792">
       <c r="B792" t="inlineStr">
         <is>
-          <t>OCT251864</t>
+          <t>OCT252200</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -21636,7 +21624,7 @@
     <row r="793">
       <c r="B793" t="inlineStr">
         <is>
-          <t>OCT251865</t>
+          <t>OCT252201</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -21661,7 +21649,7 @@
     <row r="794">
       <c r="B794" t="inlineStr">
         <is>
-          <t>OCT251866</t>
+          <t>OCT252202</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -21686,7 +21674,7 @@
     <row r="795">
       <c r="B795" t="inlineStr">
         <is>
-          <t>OCT251867</t>
+          <t>OCT252203</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -21711,7 +21699,7 @@
     <row r="796">
       <c r="B796" t="inlineStr">
         <is>
-          <t>OCT251868</t>
+          <t>OCT252204</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -21738,7 +21726,7 @@
     <row r="797">
       <c r="B797" t="inlineStr">
         <is>
-          <t>OCT251869</t>
+          <t>OCT252205</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -21765,7 +21753,7 @@
     <row r="798">
       <c r="B798" t="inlineStr">
         <is>
-          <t>OCT251870</t>
+          <t>OCT252206</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -21790,7 +21778,7 @@
     <row r="799">
       <c r="B799" t="inlineStr">
         <is>
-          <t>OCT251871</t>
+          <t>OCT252207</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -21815,7 +21803,7 @@
     <row r="800">
       <c r="B800" t="inlineStr">
         <is>
-          <t>OCT251872</t>
+          <t>OCT252208</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -21840,7 +21828,7 @@
     <row r="801">
       <c r="B801" t="inlineStr">
         <is>
-          <t>OCT251873</t>
+          <t>OCT252209</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -21865,7 +21853,7 @@
     <row r="802">
       <c r="B802" t="inlineStr">
         <is>
-          <t>OCT251874</t>
+          <t>OCT252210</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -21892,7 +21880,7 @@
     <row r="803">
       <c r="B803" t="inlineStr">
         <is>
-          <t>OCT251875</t>
+          <t>OCT252211</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -21919,7 +21907,7 @@
     <row r="804">
       <c r="B804" t="inlineStr">
         <is>
-          <t>OCT251876</t>
+          <t>OCT252212</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -21946,7 +21934,7 @@
     <row r="805">
       <c r="B805" t="inlineStr">
         <is>
-          <t>OCT251877</t>
+          <t>OCT252213</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -21971,7 +21959,7 @@
     <row r="806">
       <c r="B806" t="inlineStr">
         <is>
-          <t>OCT251878</t>
+          <t>OCT252214</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -21998,7 +21986,7 @@
     <row r="807">
       <c r="B807" t="inlineStr">
         <is>
-          <t>OCT251879</t>
+          <t>OCT252215</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -22025,7 +22013,7 @@
     <row r="808">
       <c r="B808" t="inlineStr">
         <is>
-          <t>OCT251880</t>
+          <t>OCT252216</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -22052,7 +22040,7 @@
     <row r="809">
       <c r="B809" t="inlineStr">
         <is>
-          <t>OCT251881</t>
+          <t>OCT252217</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -22079,7 +22067,7 @@
     <row r="810">
       <c r="B810" t="inlineStr">
         <is>
-          <t>OCT251882</t>
+          <t>OCT252218</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -22106,7 +22094,7 @@
     <row r="811">
       <c r="B811" t="inlineStr">
         <is>
-          <t>OCT251883</t>
+          <t>OCT252219</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -22131,7 +22119,7 @@
     <row r="812">
       <c r="B812" t="inlineStr">
         <is>
-          <t>OCT251884</t>
+          <t>OCT252220</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -22156,7 +22144,7 @@
     <row r="813">
       <c r="B813" t="inlineStr">
         <is>
-          <t>OCT251885</t>
+          <t>OCT252221</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -22181,7 +22169,7 @@
     <row r="814">
       <c r="B814" t="inlineStr">
         <is>
-          <t>OCT251886</t>
+          <t>OCT252222</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -22206,7 +22194,7 @@
     <row r="815">
       <c r="B815" t="inlineStr">
         <is>
-          <t>OCT251887</t>
+          <t>OCT252223</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -22233,7 +22221,7 @@
     <row r="816">
       <c r="B816" t="inlineStr">
         <is>
-          <t>OCT251888</t>
+          <t>OCT252224</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -22260,7 +22248,7 @@
     <row r="817">
       <c r="B817" t="inlineStr">
         <is>
-          <t>OCT251889</t>
+          <t>OCT252225</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -22285,7 +22273,7 @@
     <row r="818">
       <c r="B818" t="inlineStr">
         <is>
-          <t>OCT251890</t>
+          <t>OCT252226</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -22312,7 +22300,7 @@
     <row r="819">
       <c r="B819" t="inlineStr">
         <is>
-          <t>OCT251891</t>
+          <t>OCT252227</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -22339,7 +22327,7 @@
     <row r="820">
       <c r="B820" t="inlineStr">
         <is>
-          <t>OCT251892</t>
+          <t>OCT252228</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -22366,7 +22354,7 @@
     <row r="821">
       <c r="B821" t="inlineStr">
         <is>
-          <t>OCT251893</t>
+          <t>OCT252229</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -22393,7 +22381,7 @@
     <row r="822">
       <c r="B822" t="inlineStr">
         <is>
-          <t>OCT251894</t>
+          <t>OCT252230</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -22420,7 +22408,7 @@
     <row r="823">
       <c r="B823" t="inlineStr">
         <is>
-          <t>OCT251895</t>
+          <t>OCT252231</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -22445,7 +22433,7 @@
     <row r="824">
       <c r="B824" t="inlineStr">
         <is>
-          <t>OCT251896</t>
+          <t>OCT252232</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -22472,7 +22460,7 @@
     <row r="825">
       <c r="B825" t="inlineStr">
         <is>
-          <t>OCT251897</t>
+          <t>OCT252233</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -22497,7 +22485,7 @@
     <row r="826">
       <c r="B826" t="inlineStr">
         <is>
-          <t>OCT251898</t>
+          <t>OCT252234</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -22522,7 +22510,7 @@
     <row r="827">
       <c r="B827" t="inlineStr">
         <is>
-          <t>OCT251899</t>
+          <t>OCT252235</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -22547,7 +22535,7 @@
     <row r="828">
       <c r="B828" t="inlineStr">
         <is>
-          <t>OCT251900</t>
+          <t>OCT252236</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -22574,7 +22562,7 @@
     <row r="829">
       <c r="B829" t="inlineStr">
         <is>
-          <t>OCT251901</t>
+          <t>OCT252237</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -22601,7 +22589,7 @@
     <row r="830">
       <c r="B830" t="inlineStr">
         <is>
-          <t>OCT251902</t>
+          <t>OCT252238</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -22628,7 +22616,7 @@
     <row r="831">
       <c r="B831" t="inlineStr">
         <is>
-          <t>OCT251903</t>
+          <t>OCT252239</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -22655,7 +22643,7 @@
     <row r="832">
       <c r="B832" t="inlineStr">
         <is>
-          <t>OCT251904</t>
+          <t>OCT252240</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -22682,7 +22670,7 @@
     <row r="833">
       <c r="B833" t="inlineStr">
         <is>
-          <t>OCT251905</t>
+          <t>OCT252241</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -22707,7 +22695,7 @@
     <row r="834">
       <c r="B834" t="inlineStr">
         <is>
-          <t>OCT251906</t>
+          <t>OCT252242</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -22734,7 +22722,7 @@
     <row r="835">
       <c r="B835" t="inlineStr">
         <is>
-          <t>OCT251907</t>
+          <t>OCT252243</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -22759,7 +22747,7 @@
     <row r="836">
       <c r="B836" t="inlineStr">
         <is>
-          <t>OCT251908</t>
+          <t>OCT252244</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -22786,7 +22774,7 @@
     <row r="837">
       <c r="B837" t="inlineStr">
         <is>
-          <t>OCT251909</t>
+          <t>OCT252245</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -22813,7 +22801,7 @@
     <row r="838">
       <c r="B838" t="inlineStr">
         <is>
-          <t>OCT251910</t>
+          <t>OCT252246</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -22840,7 +22828,7 @@
     <row r="839">
       <c r="B839" t="inlineStr">
         <is>
-          <t>OCT251911</t>
+          <t>OCT252247</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -22867,7 +22855,7 @@
     <row r="840">
       <c r="B840" t="inlineStr">
         <is>
-          <t>OCT251912</t>
+          <t>OCT252248</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -22894,7 +22882,7 @@
     <row r="841">
       <c r="B841" t="inlineStr">
         <is>
-          <t>OCT251913</t>
+          <t>OCT252249</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -22921,7 +22909,7 @@
     <row r="842">
       <c r="B842" t="inlineStr">
         <is>
-          <t>OCT251914</t>
+          <t>OCT252250</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -22948,7 +22936,7 @@
     <row r="843">
       <c r="B843" t="inlineStr">
         <is>
-          <t>OCT251915</t>
+          <t>OCT252251</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -22973,7 +22961,7 @@
     <row r="844">
       <c r="B844" t="inlineStr">
         <is>
-          <t>OCT251916</t>
+          <t>OCT252252</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -22998,7 +22986,7 @@
     <row r="845">
       <c r="B845" t="inlineStr">
         <is>
-          <t>OCT251917</t>
+          <t>OCT252253</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
